--- a/research/traditional_assets/database/data/slovakia/slovakia_metals_mining.xlsx
+++ b/research/traditional_assets/database/data/slovakia/slovakia_metals_mining.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1041710588458377</v>
+        <v>0.1039878496222615</v>
       </c>
       <c r="C2">
-        <v>276.3576817378673</v>
+        <v>274.0464545571454</v>
       </c>
       <c r="D2">
-        <v>273.3376817378673</v>
+        <v>273.8164545571454</v>
       </c>
       <c r="E2">
-        <v>-92.8</v>
+        <v>-90.00999999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="G2">
         <v>3.02</v>
@@ -1445,28 +1445,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.140337</v>
       </c>
       <c r="N2">
-        <v>32.3504081632653</v>
+        <v>32.2100711632653</v>
       </c>
       <c r="O2">
-        <v>6.793585714285713</v>
+        <v>6.764114944285712</v>
       </c>
       <c r="P2">
-        <v>25.55682244897959</v>
+        <v>25.44595621897959</v>
       </c>
       <c r="Q2">
-        <v>29.22682244897959</v>
+        <v>29.11595621897958</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1041710588458377</v>
+        <v>0.1046368481032944</v>
       </c>
       <c r="T2">
-        <v>0.9842199092652959</v>
+        <v>0.9920737853089281</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>230.5194507739605</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1039878496222615</v>
+        <v>0.1038046403986852</v>
       </c>
       <c r="C3">
-        <v>274.0464545571454</v>
+        <v>271.7369075371586</v>
       </c>
       <c r="D3">
-        <v>273.8164545571454</v>
+        <v>274.2969075371586</v>
       </c>
       <c r="E3">
-        <v>-90.00999999999999</v>
+        <v>-87.22</v>
       </c>
       <c r="F3">
-        <v>2.79</v>
+        <v>5.58</v>
       </c>
       <c r="G3">
         <v>3.02</v>
@@ -1527,28 +1527,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M3">
-        <v>0.140337</v>
+        <v>0.280674</v>
       </c>
       <c r="N3">
-        <v>32.2100711632653</v>
+        <v>32.0697341632653</v>
       </c>
       <c r="O3">
-        <v>6.764114944285712</v>
+        <v>6.734644174285713</v>
       </c>
       <c r="P3">
-        <v>25.44595621897959</v>
+        <v>25.33508998897959</v>
       </c>
       <c r="Q3">
-        <v>29.11595621897958</v>
+        <v>29.00508998897959</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1046368481032944</v>
+        <v>0.1051121432639645</v>
       </c>
       <c r="T3">
-        <v>0.9920737853089281</v>
+        <v>1.000087944537124</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>230.5194507739605</v>
+        <v>115.2597253869803</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1038046403986852</v>
+        <v>0.1036214311751089</v>
       </c>
       <c r="C4">
-        <v>271.7369075371586</v>
+        <v>269.4290495377521</v>
       </c>
       <c r="D4">
-        <v>274.2969075371586</v>
+        <v>274.7790495377521</v>
       </c>
       <c r="E4">
-        <v>-87.22</v>
+        <v>-84.42999999999999</v>
       </c>
       <c r="F4">
-        <v>5.58</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G4">
         <v>3.02</v>
@@ -1609,28 +1609,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M4">
-        <v>0.280674</v>
+        <v>0.4210109999999999</v>
       </c>
       <c r="N4">
-        <v>32.0697341632653</v>
+        <v>31.9293971632653</v>
       </c>
       <c r="O4">
-        <v>6.734644174285713</v>
+        <v>6.705173404285713</v>
       </c>
       <c r="P4">
-        <v>25.33508998897959</v>
+        <v>25.22422375897959</v>
       </c>
       <c r="Q4">
-        <v>29.00508998897959</v>
+        <v>28.89422375897959</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1051121432639645</v>
+        <v>0.1055972383248546</v>
       </c>
       <c r="T4">
-        <v>1.000087944537124</v>
+        <v>1.008267344161778</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.2597253869803</v>
+        <v>76.83981692465353</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1036214311751089</v>
+        <v>0.1034382219515327</v>
       </c>
       <c r="C5">
-        <v>269.4290495377521</v>
+        <v>267.122889481174</v>
       </c>
       <c r="D5">
-        <v>274.7790495377521</v>
+        <v>275.2628894811741</v>
       </c>
       <c r="E5">
-        <v>-84.42999999999999</v>
+        <v>-81.64</v>
       </c>
       <c r="F5">
-        <v>8.369999999999999</v>
+        <v>11.16</v>
       </c>
       <c r="G5">
         <v>3.02</v>
@@ -1691,28 +1691,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M5">
-        <v>0.4210109999999999</v>
+        <v>0.561348</v>
       </c>
       <c r="N5">
-        <v>31.9293971632653</v>
+        <v>31.7890601632653</v>
       </c>
       <c r="O5">
-        <v>6.705173404285713</v>
+        <v>6.675702634285713</v>
       </c>
       <c r="P5">
-        <v>25.22422375897959</v>
+        <v>25.11335752897959</v>
       </c>
       <c r="Q5">
-        <v>28.89422375897959</v>
+        <v>28.78335752897959</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1055972383248546</v>
+        <v>0.1060924395328466</v>
       </c>
       <c r="T5">
-        <v>1.008267344161778</v>
+        <v>1.016617147945279</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.83981692465353</v>
+        <v>57.62986269349014</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1034382219515327</v>
+        <v>0.1032550127279564</v>
       </c>
       <c r="C6">
-        <v>267.122889481174</v>
+        <v>264.8184363526258</v>
       </c>
       <c r="D6">
-        <v>275.2628894811741</v>
+        <v>275.7484363526258</v>
       </c>
       <c r="E6">
-        <v>-81.64</v>
+        <v>-78.84999999999999</v>
       </c>
       <c r="F6">
-        <v>11.16</v>
+        <v>13.95</v>
       </c>
       <c r="G6">
         <v>3.02</v>
@@ -1773,28 +1773,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M6">
-        <v>0.561348</v>
+        <v>0.701685</v>
       </c>
       <c r="N6">
-        <v>31.7890601632653</v>
+        <v>31.6487231632653</v>
       </c>
       <c r="O6">
-        <v>6.675702634285713</v>
+        <v>6.646231864285713</v>
       </c>
       <c r="P6">
-        <v>25.11335752897959</v>
+        <v>25.00249129897959</v>
       </c>
       <c r="Q6">
-        <v>28.78335752897959</v>
+        <v>28.67249129897959</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1060924395328466</v>
+        <v>0.1065980660294278</v>
       </c>
       <c r="T6">
-        <v>1.016617147945279</v>
+        <v>1.02514273707159</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.62986269349014</v>
+        <v>46.1038901547921</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1032550127279564</v>
+        <v>0.1030718035043802</v>
       </c>
       <c r="C7">
-        <v>264.8184363526258</v>
+        <v>262.5156992008181</v>
       </c>
       <c r="D7">
-        <v>275.7484363526258</v>
+        <v>276.2356992008181</v>
       </c>
       <c r="E7">
-        <v>-78.84999999999999</v>
+        <v>-76.06</v>
       </c>
       <c r="F7">
-        <v>13.95</v>
+        <v>16.74</v>
       </c>
       <c r="G7">
         <v>3.02</v>
@@ -1855,28 +1855,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M7">
-        <v>0.701685</v>
+        <v>0.842022</v>
       </c>
       <c r="N7">
-        <v>31.6487231632653</v>
+        <v>31.5083861632653</v>
       </c>
       <c r="O7">
-        <v>6.646231864285713</v>
+        <v>6.616761094285713</v>
       </c>
       <c r="P7">
-        <v>25.00249129897959</v>
+        <v>24.89162506897959</v>
       </c>
       <c r="Q7">
-        <v>28.67249129897959</v>
+        <v>28.56162506897959</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1065980660294278</v>
+        <v>0.1071144505365746</v>
       </c>
       <c r="T7">
-        <v>1.02514273707159</v>
+        <v>1.033849721711227</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.1038901547921</v>
+        <v>38.41990846232675</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1030718035043802</v>
+        <v>0.1028885942808039</v>
       </c>
       <c r="C8">
-        <v>262.5156992008181</v>
+        <v>260.2146871385333</v>
       </c>
       <c r="D8">
-        <v>276.2356992008181</v>
+        <v>276.7246871385333</v>
       </c>
       <c r="E8">
-        <v>-76.06</v>
+        <v>-73.27</v>
       </c>
       <c r="F8">
-        <v>16.74</v>
+        <v>19.53</v>
       </c>
       <c r="G8">
         <v>3.02</v>
@@ -1937,28 +1937,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M8">
-        <v>0.8420219999999998</v>
+        <v>0.9823589999999999</v>
       </c>
       <c r="N8">
-        <v>31.5083861632653</v>
+        <v>31.3680491632653</v>
       </c>
       <c r="O8">
-        <v>6.616761094285713</v>
+        <v>6.587290324285713</v>
       </c>
       <c r="P8">
-        <v>24.89162506897959</v>
+        <v>24.78075883897959</v>
       </c>
       <c r="Q8">
-        <v>28.56162506897959</v>
+        <v>28.45075883897959</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1071144505365746</v>
+        <v>0.1076419400868859</v>
       </c>
       <c r="T8">
-        <v>1.033849721711227</v>
+        <v>1.042743953332361</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.41990846232677</v>
+        <v>32.93135011056579</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1028885942808039</v>
+        <v>0.1027053850572276</v>
       </c>
       <c r="C9">
-        <v>260.2146871385333</v>
+        <v>257.9154093431932</v>
       </c>
       <c r="D9">
-        <v>276.7246871385334</v>
+        <v>277.2154093431932</v>
       </c>
       <c r="E9">
-        <v>-73.27</v>
+        <v>-70.47999999999999</v>
       </c>
       <c r="F9">
-        <v>19.53</v>
+        <v>22.32</v>
       </c>
       <c r="G9">
         <v>3.02</v>
@@ -2019,28 +2019,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M9">
-        <v>0.982359</v>
+        <v>1.122696</v>
       </c>
       <c r="N9">
-        <v>31.3680491632653</v>
+        <v>31.2277121632653</v>
       </c>
       <c r="O9">
-        <v>6.587290324285713</v>
+        <v>6.557819554285713</v>
       </c>
       <c r="P9">
-        <v>24.78075883897959</v>
+        <v>24.66989260897959</v>
       </c>
       <c r="Q9">
-        <v>28.45075883897959</v>
+        <v>28.33989260897959</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1076419400868859</v>
+        <v>0.1081808968013344</v>
       </c>
       <c r="T9">
-        <v>1.042743953332361</v>
+        <v>1.051831537814825</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.93135011056579</v>
+        <v>28.81493134674507</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1027053850572276</v>
+        <v>0.1025221758336514</v>
       </c>
       <c r="C10">
-        <v>257.9154093431932</v>
+        <v>255.6178750574335</v>
       </c>
       <c r="D10">
-        <v>277.2154093431932</v>
+        <v>277.7078750574336</v>
       </c>
       <c r="E10">
-        <v>-70.47999999999999</v>
+        <v>-67.69</v>
       </c>
       <c r="F10">
-        <v>22.32</v>
+        <v>25.11</v>
       </c>
       <c r="G10">
         <v>3.02</v>
@@ -2101,28 +2101,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M10">
-        <v>1.122696</v>
+        <v>1.263033</v>
       </c>
       <c r="N10">
-        <v>31.2277121632653</v>
+        <v>31.0873751632653</v>
       </c>
       <c r="O10">
-        <v>6.557819554285713</v>
+        <v>6.528348784285713</v>
       </c>
       <c r="P10">
-        <v>24.66989260897959</v>
+        <v>24.55902637897959</v>
       </c>
       <c r="Q10">
-        <v>28.33989260897959</v>
+        <v>28.22902637897959</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1081808968013344</v>
+        <v>0.1087316987182982</v>
       </c>
       <c r="T10">
-        <v>1.051831537814825</v>
+        <v>1.061118849428771</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.81493134674507</v>
+        <v>25.61327230821784</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1025221758336514</v>
+        <v>0.1023389666100751</v>
       </c>
       <c r="C11">
-        <v>255.6178750574335</v>
+        <v>253.322093589684</v>
       </c>
       <c r="D11">
-        <v>277.7078750574336</v>
+        <v>278.202093589684</v>
       </c>
       <c r="E11">
-        <v>-67.69</v>
+        <v>-64.90000000000001</v>
       </c>
       <c r="F11">
-        <v>25.11</v>
+        <v>27.9</v>
       </c>
       <c r="G11">
         <v>3.02</v>
@@ -2183,28 +2183,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M11">
-        <v>1.263033</v>
+        <v>1.40337</v>
       </c>
       <c r="N11">
-        <v>31.0873751632653</v>
+        <v>30.9470381632653</v>
       </c>
       <c r="O11">
-        <v>6.528348784285713</v>
+        <v>6.498878014285713</v>
       </c>
       <c r="P11">
-        <v>24.55902637897959</v>
+        <v>24.44816014897959</v>
       </c>
       <c r="Q11">
-        <v>28.22902637897959</v>
+        <v>28.11816014897959</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1087316987182982</v>
+        <v>0.1092947406778612</v>
       </c>
       <c r="T11">
-        <v>1.061118849428771</v>
+        <v>1.07061254574525</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.61327230821784</v>
+        <v>23.05194507739606</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1023389666100751</v>
+        <v>0.1021557573864989</v>
       </c>
       <c r="C12">
-        <v>253.322093589684</v>
+        <v>251.0280743147547</v>
       </c>
       <c r="D12">
-        <v>278.202093589684</v>
+        <v>278.6980743147548</v>
       </c>
       <c r="E12">
-        <v>-64.89999999999999</v>
+        <v>-62.11</v>
       </c>
       <c r="F12">
-        <v>27.9</v>
+        <v>30.69</v>
       </c>
       <c r="G12">
         <v>3.02</v>
@@ -2265,28 +2265,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M12">
-        <v>1.40337</v>
+        <v>1.543707</v>
       </c>
       <c r="N12">
-        <v>30.9470381632653</v>
+        <v>30.8067011632653</v>
       </c>
       <c r="O12">
-        <v>6.498878014285713</v>
+        <v>6.469407244285712</v>
       </c>
       <c r="P12">
-        <v>24.44816014897959</v>
+        <v>24.33729391897959</v>
       </c>
       <c r="Q12">
-        <v>28.11816014897959</v>
+        <v>28.00729391897958</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1092947406778612</v>
+        <v>0.1098704352657291</v>
       </c>
       <c r="T12">
-        <v>1.07061254574525</v>
+        <v>1.080319583551986</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.05194507739606</v>
+        <v>20.95631370672368</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1021557573864989</v>
+        <v>0.1019725481629226</v>
       </c>
       <c r="C13">
-        <v>251.0280743147547</v>
+        <v>248.7358266744295</v>
       </c>
       <c r="D13">
-        <v>278.6980743147548</v>
+        <v>279.1958266744296</v>
       </c>
       <c r="E13">
-        <v>-62.11</v>
+        <v>-59.32</v>
       </c>
       <c r="F13">
-        <v>30.69</v>
+        <v>33.48</v>
       </c>
       <c r="G13">
         <v>3.02</v>
@@ -2347,28 +2347,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M13">
-        <v>1.543707</v>
+        <v>1.684044</v>
       </c>
       <c r="N13">
-        <v>30.8067011632653</v>
+        <v>30.6663641632653</v>
       </c>
       <c r="O13">
-        <v>6.469407244285712</v>
+        <v>6.439936474285712</v>
       </c>
       <c r="P13">
-        <v>24.33729391897959</v>
+        <v>24.22642768897959</v>
       </c>
       <c r="Q13">
-        <v>28.00729391897958</v>
+        <v>27.89642768897959</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1098704352657291</v>
+        <v>0.110459213821503</v>
       </c>
       <c r="T13">
-        <v>1.080319583551986</v>
+        <v>1.09024723585433</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.95631370672368</v>
+        <v>19.20995423116338</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1019725481629226</v>
+        <v>0.1017893389393464</v>
       </c>
       <c r="C14">
-        <v>248.7358266744295</v>
+        <v>246.4453601780643</v>
       </c>
       <c r="D14">
-        <v>279.1958266744296</v>
+        <v>279.6953601780643</v>
       </c>
       <c r="E14">
-        <v>-59.32</v>
+        <v>-56.52999999999999</v>
       </c>
       <c r="F14">
-        <v>33.48</v>
+        <v>36.27</v>
       </c>
       <c r="G14">
         <v>3.02</v>
@@ -2429,28 +2429,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M14">
-        <v>1.684044</v>
+        <v>1.824381</v>
       </c>
       <c r="N14">
-        <v>30.6663641632653</v>
+        <v>30.5260271632653</v>
       </c>
       <c r="O14">
-        <v>6.439936474285712</v>
+        <v>6.410465704285713</v>
       </c>
       <c r="P14">
-        <v>24.22642768897959</v>
+        <v>24.11556145897959</v>
       </c>
       <c r="Q14">
-        <v>27.89642768897959</v>
+        <v>27.78556145897959</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.110459213821503</v>
+        <v>0.1110615275164901</v>
       </c>
       <c r="T14">
-        <v>1.09024723585433</v>
+        <v>1.100403110048682</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.20995423116338</v>
+        <v>17.73226544415081</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1017893389393464</v>
+        <v>0.1016061297157701</v>
       </c>
       <c r="C15">
-        <v>246.4453601780643</v>
+        <v>244.1566844031931</v>
       </c>
       <c r="D15">
-        <v>279.6953601780643</v>
+        <v>280.1966844031932</v>
       </c>
       <c r="E15">
-        <v>-56.52999999999999</v>
+        <v>-53.73999999999999</v>
       </c>
       <c r="F15">
-        <v>36.27</v>
+        <v>39.06</v>
       </c>
       <c r="G15">
         <v>3.02</v>
@@ -2511,28 +2511,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M15">
-        <v>1.824381</v>
+        <v>1.964718</v>
       </c>
       <c r="N15">
-        <v>30.5260271632653</v>
+        <v>30.3856901632653</v>
       </c>
       <c r="O15">
-        <v>6.410465704285713</v>
+        <v>6.380994934285712</v>
       </c>
       <c r="P15">
-        <v>24.11556145897959</v>
+        <v>24.00469522897959</v>
       </c>
       <c r="Q15">
-        <v>27.78556145897959</v>
+        <v>27.67469522897959</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1110615275164901</v>
+        <v>0.1116778485067094</v>
       </c>
       <c r="T15">
-        <v>1.100403110048682</v>
+        <v>1.110795167363833</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.73226544415081</v>
+        <v>16.46567505528289</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1016061297157701</v>
+        <v>0.1014229204921938</v>
       </c>
       <c r="C16">
-        <v>244.1566844031931</v>
+        <v>241.8698089961404</v>
       </c>
       <c r="D16">
-        <v>280.1966844031932</v>
+        <v>280.6998089961404</v>
       </c>
       <c r="E16">
-        <v>-53.73999999999999</v>
+        <v>-50.94999999999999</v>
       </c>
       <c r="F16">
-        <v>39.06</v>
+        <v>41.85000000000001</v>
       </c>
       <c r="G16">
         <v>3.02</v>
@@ -2593,28 +2593,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M16">
-        <v>1.964718</v>
+        <v>2.105055</v>
       </c>
       <c r="N16">
-        <v>30.3856901632653</v>
+        <v>30.2453531632653</v>
       </c>
       <c r="O16">
-        <v>6.380994934285712</v>
+        <v>6.351524164285713</v>
       </c>
       <c r="P16">
-        <v>24.00469522897959</v>
+        <v>23.89382899897959</v>
       </c>
       <c r="Q16">
-        <v>27.67469522897959</v>
+        <v>27.56382899897959</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1116778485067094</v>
+        <v>0.1123086711672869</v>
       </c>
       <c r="T16">
-        <v>1.110795167363833</v>
+        <v>1.121431743674634</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.46567505528289</v>
+        <v>15.3679633849307</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1014229204921938</v>
+        <v>0.1012397112686176</v>
       </c>
       <c r="C17">
-        <v>241.8698089961404</v>
+        <v>239.5847436726391</v>
       </c>
       <c r="D17">
-        <v>280.6998089961404</v>
+        <v>281.2047436726391</v>
       </c>
       <c r="E17">
-        <v>-50.95</v>
+        <v>-48.16</v>
       </c>
       <c r="F17">
-        <v>41.85</v>
+        <v>44.64</v>
       </c>
       <c r="G17">
         <v>3.02</v>
@@ -2675,28 +2675,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M17">
-        <v>2.105055</v>
+        <v>2.245392</v>
       </c>
       <c r="N17">
-        <v>30.2453531632653</v>
+        <v>30.1050161632653</v>
       </c>
       <c r="O17">
-        <v>6.351524164285713</v>
+        <v>6.322053394285713</v>
       </c>
       <c r="P17">
-        <v>23.89382899897959</v>
+        <v>23.78296276897959</v>
       </c>
       <c r="Q17">
-        <v>27.56382899897959</v>
+        <v>27.45296276897959</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1123086711672869</v>
+        <v>0.1129545134150209</v>
       </c>
       <c r="T17">
-        <v>1.121431743674634</v>
+        <v>1.132321571802359</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.3679633849307</v>
+        <v>14.40746567337253</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1012397112686176</v>
+        <v>0.1010565020450413</v>
       </c>
       <c r="C18">
-        <v>239.5847436726391</v>
+        <v>237.3014982184565</v>
       </c>
       <c r="D18">
-        <v>281.2047436726391</v>
+        <v>281.7114982184565</v>
       </c>
       <c r="E18">
-        <v>-48.16</v>
+        <v>-45.36999999999999</v>
       </c>
       <c r="F18">
-        <v>44.64</v>
+        <v>47.43000000000001</v>
       </c>
       <c r="G18">
         <v>3.02</v>
@@ -2757,28 +2757,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M18">
-        <v>2.245392</v>
+        <v>2.385729</v>
       </c>
       <c r="N18">
-        <v>30.1050161632653</v>
+        <v>29.9646791632653</v>
       </c>
       <c r="O18">
-        <v>6.322053394285713</v>
+        <v>6.292582624285712</v>
       </c>
       <c r="P18">
-        <v>23.78296276897959</v>
+        <v>23.67209653897959</v>
       </c>
       <c r="Q18">
-        <v>27.45296276897959</v>
+        <v>27.34209653897959</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1129545134150209</v>
+        <v>0.1136159181265558</v>
       </c>
       <c r="T18">
-        <v>1.132321571802359</v>
+        <v>1.143473805427138</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.40746567337253</v>
+        <v>13.55996769258591</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1010565020450413</v>
+        <v>0.1010865928214651</v>
       </c>
       <c r="C19">
-        <v>237.3014982184565</v>
+        <v>234.4281421696025</v>
       </c>
       <c r="D19">
-        <v>281.7114982184565</v>
+        <v>281.6281421696025</v>
       </c>
       <c r="E19">
-        <v>-45.36999999999999</v>
+        <v>-42.57999999999999</v>
       </c>
       <c r="F19">
-        <v>47.43000000000001</v>
+        <v>50.22000000000001</v>
       </c>
       <c r="G19">
         <v>3.02</v>
@@ -2839,45 +2839,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M19">
-        <v>2.385729</v>
+        <v>2.601396</v>
       </c>
       <c r="N19">
-        <v>29.9646791632653</v>
+        <v>29.7490121632653</v>
       </c>
       <c r="O19">
-        <v>6.292582624285712</v>
+        <v>6.247292554285712</v>
       </c>
       <c r="P19">
-        <v>23.67209653897959</v>
+        <v>23.50171960897958</v>
       </c>
       <c r="Q19">
-        <v>27.34209653897959</v>
+        <v>27.17171960897959</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1136159181265558</v>
+        <v>0.1142934546603232</v>
       </c>
       <c r="T19">
-        <v>1.143473805427138</v>
+        <v>1.154898044750083</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.21</v>
       </c>
       <c r="W19">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.55996769258591</v>
+        <v>12.43578761682777</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1010865928214651</v>
+        <v>0.1009152335978888</v>
       </c>
       <c r="C20">
-        <v>234.4281421696024</v>
+        <v>232.1134939272583</v>
       </c>
       <c r="D20">
-        <v>281.6281421696024</v>
+        <v>282.1034939272583</v>
       </c>
       <c r="E20">
-        <v>-42.58</v>
+        <v>-39.79</v>
       </c>
       <c r="F20">
-        <v>50.22</v>
+        <v>53.01</v>
       </c>
       <c r="G20">
         <v>3.02</v>
@@ -2921,28 +2921,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M20">
-        <v>2.601396</v>
+        <v>2.745918</v>
       </c>
       <c r="N20">
-        <v>29.7490121632653</v>
+        <v>29.6044901632653</v>
       </c>
       <c r="O20">
-        <v>6.247292554285712</v>
+        <v>6.216942934285713</v>
       </c>
       <c r="P20">
-        <v>23.50171960897958</v>
+        <v>23.38754722897959</v>
       </c>
       <c r="Q20">
-        <v>27.17171960897959</v>
+        <v>27.05754722897959</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1142934546603232</v>
+        <v>0.1149877204912207</v>
       </c>
       <c r="T20">
-        <v>1.154898044750083</v>
+        <v>1.16660436405631</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.43578761682777</v>
+        <v>11.7812724791</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1009152335978888</v>
+        <v>0.1007438743743126</v>
       </c>
       <c r="C21">
-        <v>232.1134939272583</v>
+        <v>229.8004530621212</v>
       </c>
       <c r="D21">
-        <v>282.1034939272583</v>
+        <v>282.5804530621213</v>
       </c>
       <c r="E21">
-        <v>-39.79</v>
+        <v>-36.99999999999999</v>
       </c>
       <c r="F21">
-        <v>53.01</v>
+        <v>55.8</v>
       </c>
       <c r="G21">
         <v>3.02</v>
@@ -3003,28 +3003,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M21">
-        <v>2.745918</v>
+        <v>2.89044</v>
       </c>
       <c r="N21">
-        <v>29.6044901632653</v>
+        <v>29.4599681632653</v>
       </c>
       <c r="O21">
-        <v>6.216942934285713</v>
+        <v>6.186593314285712</v>
       </c>
       <c r="P21">
-        <v>23.38754722897959</v>
+        <v>23.27337484897959</v>
       </c>
       <c r="Q21">
-        <v>27.05754722897959</v>
+        <v>26.94337484897959</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1149877204912207</v>
+        <v>0.1156993429678907</v>
       </c>
       <c r="T21">
-        <v>1.16660436405631</v>
+        <v>1.178603341345192</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.7812724791</v>
+        <v>11.19220885514499</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1007438743743126</v>
+        <v>0.1005725151507363</v>
       </c>
       <c r="C22">
-        <v>229.8004530621212</v>
+        <v>227.4890277408923</v>
       </c>
       <c r="D22">
-        <v>282.5804530621213</v>
+        <v>283.0590277408924</v>
       </c>
       <c r="E22">
-        <v>-36.99999999999999</v>
+        <v>-34.20999999999999</v>
       </c>
       <c r="F22">
-        <v>55.8</v>
+        <v>58.59</v>
       </c>
       <c r="G22">
         <v>3.02</v>
@@ -3085,28 +3085,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M22">
-        <v>2.89044</v>
+        <v>3.034962</v>
       </c>
       <c r="N22">
-        <v>29.4599681632653</v>
+        <v>29.3154461632653</v>
       </c>
       <c r="O22">
-        <v>6.186593314285712</v>
+        <v>6.156243694285712</v>
       </c>
       <c r="P22">
-        <v>23.27337484897959</v>
+        <v>23.15920246897959</v>
       </c>
       <c r="Q22">
-        <v>26.94337484897959</v>
+        <v>26.82920246897959</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1156993429678907</v>
+        <v>0.1164289812034636</v>
       </c>
       <c r="T22">
-        <v>1.178603341345192</v>
+        <v>1.190906090211008</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.19220885514499</v>
+        <v>10.65924652870952</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1005725151507363</v>
+        <v>0.10040115592716</v>
       </c>
       <c r="C23">
-        <v>227.4890277408923</v>
+        <v>225.1792261856907</v>
       </c>
       <c r="D23">
-        <v>283.0590277408924</v>
+        <v>283.5392261856907</v>
       </c>
       <c r="E23">
-        <v>-34.21</v>
+        <v>-31.41999999999999</v>
       </c>
       <c r="F23">
-        <v>58.59</v>
+        <v>61.38</v>
       </c>
       <c r="G23">
         <v>3.02</v>
@@ -3167,28 +3167,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M23">
-        <v>3.034962</v>
+        <v>3.179484</v>
       </c>
       <c r="N23">
-        <v>29.3154461632653</v>
+        <v>29.1709241632653</v>
       </c>
       <c r="O23">
-        <v>6.156243694285712</v>
+        <v>6.125894074285713</v>
       </c>
       <c r="P23">
-        <v>23.15920246897959</v>
+        <v>23.04503008897959</v>
       </c>
       <c r="Q23">
-        <v>26.82920246897959</v>
+        <v>26.71503008897959</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1164289812034636</v>
+        <v>0.1171773281117436</v>
       </c>
       <c r="T23">
-        <v>1.190906090211008</v>
+        <v>1.203524294175948</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.65924652870952</v>
+        <v>10.17473532285909</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.10040115592716</v>
+        <v>0.1005386867035838</v>
       </c>
       <c r="C24">
-        <v>225.1792261856907</v>
+        <v>222.0036960044304</v>
       </c>
       <c r="D24">
-        <v>283.5392261856907</v>
+        <v>283.1536960044305</v>
       </c>
       <c r="E24">
-        <v>-31.41999999999999</v>
+        <v>-28.63</v>
       </c>
       <c r="F24">
-        <v>61.38</v>
+        <v>64.17</v>
       </c>
       <c r="G24">
         <v>3.02</v>
@@ -3249,45 +3249,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M24">
-        <v>3.179484</v>
+        <v>3.433095</v>
       </c>
       <c r="N24">
-        <v>29.1709241632653</v>
+        <v>28.9173131632653</v>
       </c>
       <c r="O24">
-        <v>6.125894074285713</v>
+        <v>6.072635764285712</v>
       </c>
       <c r="P24">
-        <v>23.04503008897959</v>
+        <v>22.84467739897958</v>
       </c>
       <c r="Q24">
-        <v>26.71503008897959</v>
+        <v>26.51467739897959</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1171773281117436</v>
+        <v>0.1179451126020568</v>
       </c>
       <c r="T24">
-        <v>1.203524294175948</v>
+        <v>1.216470243698418</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.21</v>
       </c>
       <c r="W24">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.17473532285909</v>
+        <v>9.423103107623092</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1005386867035838</v>
+        <v>0.1003807574800075</v>
       </c>
       <c r="C25">
-        <v>222.0036960044304</v>
+        <v>219.6564971140196</v>
       </c>
       <c r="D25">
-        <v>283.1536960044305</v>
+        <v>283.5964971140196</v>
       </c>
       <c r="E25">
-        <v>-28.63</v>
+        <v>-25.83999999999999</v>
       </c>
       <c r="F25">
-        <v>64.17</v>
+        <v>66.96000000000001</v>
       </c>
       <c r="G25">
         <v>3.02</v>
@@ -3331,28 +3331,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M25">
-        <v>3.433095</v>
+        <v>3.58236</v>
       </c>
       <c r="N25">
-        <v>28.9173131632653</v>
+        <v>28.7680481632653</v>
       </c>
       <c r="O25">
-        <v>6.072635764285712</v>
+        <v>6.041290114285712</v>
       </c>
       <c r="P25">
-        <v>22.84467739897958</v>
+        <v>22.72675804897959</v>
       </c>
       <c r="Q25">
-        <v>26.51467739897959</v>
+        <v>26.39675804897958</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1179451126020568</v>
+        <v>0.1187331019473783</v>
       </c>
       <c r="T25">
-        <v>1.216470243698418</v>
+        <v>1.229756876103059</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.423103107623092</v>
+        <v>9.030473811472129</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1003807574800075</v>
+        <v>0.1002228282564312</v>
       </c>
       <c r="C26">
-        <v>219.6564971140196</v>
+        <v>217.310685314281</v>
       </c>
       <c r="D26">
-        <v>283.5964971140196</v>
+        <v>284.0406853142811</v>
       </c>
       <c r="E26">
-        <v>-25.84</v>
+        <v>-23.05</v>
       </c>
       <c r="F26">
-        <v>66.95999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="G26">
         <v>3.02</v>
@@ -3413,28 +3413,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M26">
-        <v>3.58236</v>
+        <v>3.731625</v>
       </c>
       <c r="N26">
-        <v>28.7680481632653</v>
+        <v>28.6187831632653</v>
       </c>
       <c r="O26">
-        <v>6.041290114285712</v>
+        <v>6.009944464285713</v>
       </c>
       <c r="P26">
-        <v>22.72675804897959</v>
+        <v>22.60883869897959</v>
       </c>
       <c r="Q26">
-        <v>26.39675804897958</v>
+        <v>26.27883869897958</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1187331019473783</v>
+        <v>0.1195421043419083</v>
       </c>
       <c r="T26">
-        <v>1.229756876103059</v>
+        <v>1.243397818705157</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.030473811472131</v>
+        <v>8.669254859013245</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1002228282564312</v>
+        <v>0.100064899032855</v>
       </c>
       <c r="C27">
-        <v>217.310685314281</v>
+        <v>214.9662671331079</v>
       </c>
       <c r="D27">
-        <v>284.0406853142811</v>
+        <v>284.4862671331079</v>
       </c>
       <c r="E27">
-        <v>-23.05</v>
+        <v>-20.25999999999999</v>
       </c>
       <c r="F27">
-        <v>69.75</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="G27">
         <v>3.02</v>
@@ -3495,28 +3495,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M27">
-        <v>3.731625</v>
+        <v>3.88089</v>
       </c>
       <c r="N27">
-        <v>28.6187831632653</v>
+        <v>28.4695181632653</v>
       </c>
       <c r="O27">
-        <v>6.009944464285713</v>
+        <v>5.978598814285712</v>
       </c>
       <c r="P27">
-        <v>22.60883869897959</v>
+        <v>22.49091934897959</v>
       </c>
       <c r="Q27">
-        <v>26.27883869897958</v>
+        <v>26.16091934897959</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1195421043419083</v>
+        <v>0.1203729716660202</v>
       </c>
       <c r="T27">
-        <v>1.243397818705157</v>
+        <v>1.257407435431636</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.669254859013245</v>
+        <v>8.335821979820427</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.100064899032855</v>
+        <v>0.09990696980927873</v>
       </c>
       <c r="C28">
-        <v>214.9662671331079</v>
+        <v>212.623249139419</v>
       </c>
       <c r="D28">
-        <v>284.4862671331079</v>
+        <v>284.933249139419</v>
       </c>
       <c r="E28">
-        <v>-20.25999999999999</v>
+        <v>-17.47</v>
       </c>
       <c r="F28">
-        <v>72.54000000000001</v>
+        <v>75.33</v>
       </c>
       <c r="G28">
         <v>3.02</v>
@@ -3577,28 +3577,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M28">
-        <v>3.88089</v>
+        <v>4.030155</v>
       </c>
       <c r="N28">
-        <v>28.4695181632653</v>
+        <v>28.3202531632653</v>
       </c>
       <c r="O28">
-        <v>5.978598814285712</v>
+        <v>5.947253164285713</v>
       </c>
       <c r="P28">
-        <v>22.49091934897959</v>
+        <v>22.37299999897959</v>
       </c>
       <c r="Q28">
-        <v>26.16091934897959</v>
+        <v>26.04299999897959</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1203729716660202</v>
+        <v>0.121226602478464</v>
       </c>
       <c r="T28">
-        <v>1.257407435431636</v>
+        <v>1.271800877273909</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.335821979820427</v>
+        <v>8.027087832419671</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09990696980927873</v>
+        <v>0.09974904058570247</v>
       </c>
       <c r="C29">
-        <v>212.623249139419</v>
+        <v>210.2816379434825</v>
       </c>
       <c r="D29">
-        <v>284.933249139419</v>
+        <v>285.3816379434825</v>
       </c>
       <c r="E29">
-        <v>-17.47</v>
+        <v>-14.67999999999999</v>
       </c>
       <c r="F29">
-        <v>75.33</v>
+        <v>78.12</v>
       </c>
       <c r="G29">
         <v>3.02</v>
@@ -3659,28 +3659,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M29">
-        <v>4.030155</v>
+        <v>4.17942</v>
       </c>
       <c r="N29">
-        <v>28.3202531632653</v>
+        <v>28.1709881632653</v>
       </c>
       <c r="O29">
-        <v>5.947253164285713</v>
+        <v>5.915907514285712</v>
       </c>
       <c r="P29">
-        <v>22.37299999897959</v>
+        <v>22.25508064897959</v>
       </c>
       <c r="Q29">
-        <v>26.04299999897959</v>
+        <v>25.92508064897959</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.121226602478464</v>
+        <v>0.1221039452579201</v>
       </c>
       <c r="T29">
-        <v>1.271800877273909</v>
+        <v>1.286594136945134</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.027087832419671</v>
+        <v>7.740406124118968</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09974904058570247</v>
+        <v>0.09977439136212622</v>
       </c>
       <c r="C30">
-        <v>210.2816379434825</v>
+        <v>207.4195675770825</v>
       </c>
       <c r="D30">
-        <v>285.3816379434825</v>
+        <v>285.3095675770825</v>
       </c>
       <c r="E30">
-        <v>-14.67999999999999</v>
+        <v>-11.88999999999999</v>
       </c>
       <c r="F30">
-        <v>78.12</v>
+        <v>80.91000000000001</v>
       </c>
       <c r="G30">
         <v>3.02</v>
@@ -3741,45 +3741,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M30">
-        <v>4.17942</v>
+        <v>4.393413000000001</v>
       </c>
       <c r="N30">
-        <v>28.1709881632653</v>
+        <v>27.9569951632653</v>
       </c>
       <c r="O30">
-        <v>5.915907514285712</v>
+        <v>5.870968984285712</v>
       </c>
       <c r="P30">
-        <v>22.25508064897959</v>
+        <v>22.08602617897959</v>
       </c>
       <c r="Q30">
-        <v>25.92508064897959</v>
+        <v>25.75602617897959</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1221039452579201</v>
+        <v>0.1230060019184876</v>
       </c>
       <c r="T30">
-        <v>1.286594136945134</v>
+        <v>1.301804108156394</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.21</v>
       </c>
       <c r="W30">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.740406124118968</v>
+        <v>7.363388819413356</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09977439136212621</v>
+        <v>0.09962278213854994</v>
       </c>
       <c r="C31">
-        <v>207.4195675770826</v>
+        <v>205.0611242252605</v>
       </c>
       <c r="D31">
-        <v>285.3095675770826</v>
+        <v>285.7411242252605</v>
       </c>
       <c r="E31">
-        <v>-11.89</v>
+        <v>-9.099999999999994</v>
       </c>
       <c r="F31">
-        <v>80.91</v>
+        <v>83.7</v>
       </c>
       <c r="G31">
         <v>3.02</v>
@@ -3823,28 +3823,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M31">
-        <v>4.393413</v>
+        <v>4.544910000000001</v>
       </c>
       <c r="N31">
-        <v>27.9569951632653</v>
+        <v>27.8054981632653</v>
       </c>
       <c r="O31">
-        <v>5.870968984285713</v>
+        <v>5.839154614285713</v>
       </c>
       <c r="P31">
-        <v>22.08602617897959</v>
+        <v>21.96634354897959</v>
       </c>
       <c r="Q31">
-        <v>25.75602617897959</v>
+        <v>25.63634354897959</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1230060019184876</v>
+        <v>0.1239338316264999</v>
       </c>
       <c r="T31">
-        <v>1.301804108156394</v>
+        <v>1.317448649973689</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.363388819413359</v>
+        <v>7.117942525432912</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09962278213854994</v>
+        <v>0.09947117291497368</v>
       </c>
       <c r="C32">
-        <v>205.0611242252605</v>
+        <v>202.703988388469</v>
       </c>
       <c r="D32">
-        <v>285.7411242252605</v>
+        <v>286.1739883884691</v>
       </c>
       <c r="E32">
-        <v>-9.099999999999994</v>
+        <v>-6.310000000000002</v>
       </c>
       <c r="F32">
-        <v>83.7</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G32">
         <v>3.02</v>
@@ -3905,28 +3905,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M32">
-        <v>4.544910000000001</v>
+        <v>4.696407</v>
       </c>
       <c r="N32">
-        <v>27.8054981632653</v>
+        <v>27.6540011632653</v>
       </c>
       <c r="O32">
-        <v>5.839154614285713</v>
+        <v>5.807340244285712</v>
       </c>
       <c r="P32">
-        <v>21.96634354897959</v>
+        <v>21.84666091897959</v>
       </c>
       <c r="Q32">
-        <v>25.63634354897959</v>
+        <v>25.51666091897959</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1239338316264999</v>
+        <v>0.1248885549492372</v>
       </c>
       <c r="T32">
-        <v>1.317448649973689</v>
+        <v>1.333546656771196</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.117942525432912</v>
+        <v>6.8883314762254</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09947117291497368</v>
+        <v>0.09931956369139741</v>
       </c>
       <c r="C33">
-        <v>202.703988388469</v>
+        <v>200.3481660179175</v>
       </c>
       <c r="D33">
-        <v>286.1739883884691</v>
+        <v>286.6081660179175</v>
       </c>
       <c r="E33">
-        <v>-6.310000000000002</v>
+        <v>-3.519999999999996</v>
       </c>
       <c r="F33">
-        <v>86.48999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="G33">
         <v>3.02</v>
@@ -3987,28 +3987,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M33">
-        <v>4.696407</v>
+        <v>4.847904</v>
       </c>
       <c r="N33">
-        <v>27.6540011632653</v>
+        <v>27.5025041632653</v>
       </c>
       <c r="O33">
-        <v>5.807340244285712</v>
+        <v>5.775525874285713</v>
       </c>
       <c r="P33">
-        <v>21.84666091897959</v>
+        <v>21.72697828897959</v>
       </c>
       <c r="Q33">
-        <v>25.51666091897959</v>
+        <v>25.39697828897959</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1248885549492372</v>
+        <v>0.1258713583697021</v>
       </c>
       <c r="T33">
-        <v>1.333546656771196</v>
+        <v>1.350118134356865</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.8883314762254</v>
+        <v>6.673071117593356</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09931956369139741</v>
+        <v>0.09916795446782116</v>
       </c>
       <c r="C34">
-        <v>200.3481660179175</v>
+        <v>197.9936631009865</v>
       </c>
       <c r="D34">
-        <v>286.6081660179175</v>
+        <v>287.0436631009865</v>
       </c>
       <c r="E34">
-        <v>-3.519999999999996</v>
+        <v>-0.7299999999999898</v>
       </c>
       <c r="F34">
-        <v>89.28</v>
+        <v>92.07000000000001</v>
       </c>
       <c r="G34">
         <v>3.02</v>
@@ -4069,28 +4069,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M34">
-        <v>4.847904</v>
+        <v>4.999401000000001</v>
       </c>
       <c r="N34">
-        <v>27.5025041632653</v>
+        <v>27.3510071632653</v>
       </c>
       <c r="O34">
-        <v>5.775525874285713</v>
+        <v>5.743711504285713</v>
       </c>
       <c r="P34">
-        <v>21.72697828897959</v>
+        <v>21.60729565897959</v>
       </c>
       <c r="Q34">
-        <v>25.39697828897959</v>
+        <v>25.27729565897959</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1258713583697021</v>
+        <v>0.1268834992057032</v>
       </c>
       <c r="T34">
-        <v>1.350118134356865</v>
+        <v>1.36718428291524</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.673071117593356</v>
+        <v>6.470856841302647</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09916795446782116</v>
+        <v>0.09901634524424491</v>
       </c>
       <c r="C35">
-        <v>197.9936631009865</v>
+        <v>195.6404856615027</v>
       </c>
       <c r="D35">
-        <v>287.0436631009865</v>
+        <v>287.4804856615028</v>
       </c>
       <c r="E35">
-        <v>-0.7299999999999898</v>
+        <v>2.060000000000016</v>
       </c>
       <c r="F35">
-        <v>92.07000000000001</v>
+        <v>94.86000000000001</v>
       </c>
       <c r="G35">
         <v>3.02</v>
@@ -4151,28 +4151,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M35">
-        <v>4.999401000000001</v>
+        <v>5.150898000000001</v>
       </c>
       <c r="N35">
-        <v>27.3510071632653</v>
+        <v>27.1995101632653</v>
       </c>
       <c r="O35">
-        <v>5.743711504285713</v>
+        <v>5.711897134285713</v>
       </c>
       <c r="P35">
-        <v>21.60729565897959</v>
+        <v>21.48761302897958</v>
       </c>
       <c r="Q35">
-        <v>25.27729565897959</v>
+        <v>25.15761302897958</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1268834992057032</v>
+        <v>0.1279263109761287</v>
       </c>
       <c r="T35">
-        <v>1.36718428291524</v>
+        <v>1.384767587490536</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.470856841302647</v>
+        <v>6.280537522440804</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09901634524424491</v>
+        <v>0.09914123602066864</v>
       </c>
       <c r="C36">
-        <v>195.6404856615027</v>
+        <v>192.4905489751026</v>
       </c>
       <c r="D36">
-        <v>287.4804856615028</v>
+        <v>287.1205489751026</v>
       </c>
       <c r="E36">
-        <v>2.060000000000016</v>
+        <v>4.850000000000009</v>
       </c>
       <c r="F36">
-        <v>94.86000000000001</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="G36">
         <v>3.02</v>
@@ -4233,45 +4233,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M36">
-        <v>5.150898000000001</v>
+        <v>5.400045</v>
       </c>
       <c r="N36">
-        <v>27.1995101632653</v>
+        <v>26.9503631632653</v>
       </c>
       <c r="O36">
-        <v>5.711897134285713</v>
+        <v>5.659576264285713</v>
       </c>
       <c r="P36">
-        <v>21.48761302897958</v>
+        <v>21.29078689897959</v>
       </c>
       <c r="Q36">
-        <v>25.15761302897958</v>
+        <v>24.96078689897959</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1279263109761287</v>
+        <v>0.1290012092625672</v>
       </c>
       <c r="T36">
-        <v>1.384767587490536</v>
+        <v>1.402891916821995</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.21</v>
       </c>
       <c r="W36">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.280537522440804</v>
+        <v>5.990766403477249</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09914123602066864</v>
+        <v>0.09899752679709238</v>
       </c>
       <c r="C37">
-        <v>192.4905489751026</v>
+        <v>190.114798896307</v>
       </c>
       <c r="D37">
-        <v>287.1205489751026</v>
+        <v>287.534798896307</v>
       </c>
       <c r="E37">
-        <v>4.850000000000009</v>
+        <v>7.640000000000015</v>
       </c>
       <c r="F37">
-        <v>97.65000000000001</v>
+        <v>100.44</v>
       </c>
       <c r="G37">
         <v>3.02</v>
@@ -4315,28 +4315,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M37">
-        <v>5.400045</v>
+        <v>5.554332</v>
       </c>
       <c r="N37">
-        <v>26.9503631632653</v>
+        <v>26.7960761632653</v>
       </c>
       <c r="O37">
-        <v>5.659576264285713</v>
+        <v>5.627175994285713</v>
       </c>
       <c r="P37">
-        <v>21.29078689897959</v>
+        <v>21.16890016897958</v>
       </c>
       <c r="Q37">
-        <v>24.96078689897959</v>
+        <v>24.83890016897958</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1290012092625672</v>
+        <v>0.1301096981204569</v>
       </c>
       <c r="T37">
-        <v>1.402891916821995</v>
+        <v>1.421582631445062</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.990766403477249</v>
+        <v>5.82435622560288</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09899752679709239</v>
+        <v>0.09885381757351613</v>
       </c>
       <c r="C38">
-        <v>190.1147988963069</v>
+        <v>187.7402458822272</v>
       </c>
       <c r="D38">
-        <v>287.5347988963069</v>
+        <v>287.9502458822272</v>
       </c>
       <c r="E38">
-        <v>7.640000000000001</v>
+        <v>10.43000000000001</v>
       </c>
       <c r="F38">
-        <v>100.44</v>
+        <v>103.23</v>
       </c>
       <c r="G38">
         <v>3.02</v>
@@ -4397,28 +4397,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M38">
-        <v>5.554332</v>
+        <v>5.708619000000001</v>
       </c>
       <c r="N38">
-        <v>26.7960761632653</v>
+        <v>26.6417891632653</v>
       </c>
       <c r="O38">
-        <v>5.627175994285713</v>
+        <v>5.594775724285713</v>
       </c>
       <c r="P38">
-        <v>21.16890016897958</v>
+        <v>21.04701343897959</v>
       </c>
       <c r="Q38">
-        <v>24.83890016897958</v>
+        <v>24.71701343897959</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1301096981204569</v>
+        <v>0.1312533771008192</v>
       </c>
       <c r="T38">
-        <v>1.421582631445062</v>
+        <v>1.440866702087908</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.82435622560288</v>
+        <v>5.666941192478478</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09885381757351613</v>
+        <v>0.09871010834993989</v>
       </c>
       <c r="C39">
-        <v>187.7402458822272</v>
+        <v>185.3668951291372</v>
       </c>
       <c r="D39">
-        <v>287.9502458822272</v>
+        <v>288.3668951291372</v>
       </c>
       <c r="E39">
-        <v>10.43000000000001</v>
+        <v>13.22</v>
       </c>
       <c r="F39">
-        <v>103.23</v>
+        <v>106.02</v>
       </c>
       <c r="G39">
         <v>3.02</v>
@@ -4479,28 +4479,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M39">
-        <v>5.708619000000001</v>
+        <v>5.862906</v>
       </c>
       <c r="N39">
-        <v>26.6417891632653</v>
+        <v>26.4875021632653</v>
       </c>
       <c r="O39">
-        <v>5.594775724285713</v>
+        <v>5.562375454285713</v>
       </c>
       <c r="P39">
-        <v>21.04701343897959</v>
+        <v>20.92512670897959</v>
       </c>
       <c r="Q39">
-        <v>24.71701343897959</v>
+        <v>24.59512670897958</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1312533771008192</v>
+        <v>0.1324339489515159</v>
       </c>
       <c r="T39">
-        <v>1.440866702087908</v>
+        <v>1.460772839525686</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.666941192478478</v>
+        <v>5.517811161097466</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09871010834993989</v>
+        <v>0.09856639912636363</v>
       </c>
       <c r="C40">
-        <v>185.3668951291372</v>
+        <v>182.9947518634295</v>
       </c>
       <c r="D40">
-        <v>288.3668951291372</v>
+        <v>288.7847518634296</v>
       </c>
       <c r="E40">
-        <v>13.22</v>
+        <v>16.01000000000001</v>
       </c>
       <c r="F40">
-        <v>106.02</v>
+        <v>108.81</v>
       </c>
       <c r="G40">
         <v>3.02</v>
@@ -4561,28 +4561,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M40">
-        <v>5.862906</v>
+        <v>6.017193000000001</v>
       </c>
       <c r="N40">
-        <v>26.4875021632653</v>
+        <v>26.3332151632653</v>
       </c>
       <c r="O40">
-        <v>5.562375454285713</v>
+        <v>5.529975184285713</v>
       </c>
       <c r="P40">
-        <v>20.92512670897959</v>
+        <v>20.80323997897959</v>
       </c>
       <c r="Q40">
-        <v>24.59512670897958</v>
+        <v>24.47323997897958</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1324339489515159</v>
+        <v>0.1336532280760059</v>
       </c>
       <c r="T40">
-        <v>1.460772839525686</v>
+        <v>1.481331637207325</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.517811161097466</v>
+        <v>5.376328823633428</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09856639912636363</v>
+        <v>0.09842268990278737</v>
       </c>
       <c r="C41">
-        <v>182.9947518634295</v>
+        <v>180.6238213418335</v>
       </c>
       <c r="D41">
-        <v>288.7847518634296</v>
+        <v>289.2038213418335</v>
       </c>
       <c r="E41">
-        <v>16.01000000000001</v>
+        <v>18.80000000000001</v>
       </c>
       <c r="F41">
-        <v>108.81</v>
+        <v>111.6</v>
       </c>
       <c r="G41">
         <v>3.02</v>
@@ -4643,28 +4643,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M41">
-        <v>6.017193000000001</v>
+        <v>6.171480000000001</v>
       </c>
       <c r="N41">
-        <v>26.3332151632653</v>
+        <v>26.1789281632653</v>
       </c>
       <c r="O41">
-        <v>5.529975184285713</v>
+        <v>5.497574914285712</v>
       </c>
       <c r="P41">
-        <v>20.80323997897959</v>
+        <v>20.68135324897958</v>
       </c>
       <c r="Q41">
-        <v>24.47323997897958</v>
+        <v>24.35135324897958</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1336532280760059</v>
+        <v>0.1349131498379789</v>
       </c>
       <c r="T41">
-        <v>1.481331637207325</v>
+        <v>1.502575728145018</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.376328823633428</v>
+        <v>5.241920603042591</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09842268990278737</v>
+        <v>0.09827898067921109</v>
       </c>
       <c r="C42">
-        <v>180.6238213418335</v>
+        <v>178.2541088516363</v>
       </c>
       <c r="D42">
-        <v>289.2038213418335</v>
+        <v>289.6241088516363</v>
       </c>
       <c r="E42">
-        <v>18.80000000000001</v>
+        <v>21.59000000000002</v>
       </c>
       <c r="F42">
-        <v>111.6</v>
+        <v>114.39</v>
       </c>
       <c r="G42">
         <v>3.02</v>
@@ -4725,28 +4725,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M42">
-        <v>6.171480000000001</v>
+        <v>6.325767000000001</v>
       </c>
       <c r="N42">
-        <v>26.1789281632653</v>
+        <v>26.0246411632653</v>
       </c>
       <c r="O42">
-        <v>5.497574914285712</v>
+        <v>5.465174644285713</v>
       </c>
       <c r="P42">
-        <v>20.68135324897958</v>
+        <v>20.55946651897959</v>
       </c>
       <c r="Q42">
-        <v>24.35135324897958</v>
+        <v>24.22946651897959</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1349131498379789</v>
+        <v>0.1362157808122222</v>
       </c>
       <c r="T42">
-        <v>1.502575728145018</v>
+        <v>1.524539957758566</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.241920603042591</v>
+        <v>5.114068881017163</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09827898067921109</v>
+        <v>0.09813527145563483</v>
       </c>
       <c r="C43">
-        <v>178.2541088516363</v>
+        <v>175.8856197109046</v>
       </c>
       <c r="D43">
-        <v>289.6241088516363</v>
+        <v>290.0456197109046</v>
       </c>
       <c r="E43">
-        <v>21.59000000000002</v>
+        <v>24.38000000000001</v>
       </c>
       <c r="F43">
-        <v>114.39</v>
+        <v>117.18</v>
       </c>
       <c r="G43">
         <v>3.02</v>
@@ -4807,28 +4807,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M43">
-        <v>6.325767000000001</v>
+        <v>6.480054000000001</v>
       </c>
       <c r="N43">
-        <v>26.0246411632653</v>
+        <v>25.8703541632653</v>
       </c>
       <c r="O43">
-        <v>5.465174644285713</v>
+        <v>5.432774374285712</v>
       </c>
       <c r="P43">
-        <v>20.55946651897959</v>
+        <v>20.43757978897958</v>
       </c>
       <c r="Q43">
-        <v>24.22946651897959</v>
+        <v>24.10757978897959</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1362157808122222</v>
+        <v>0.1375633300959221</v>
       </c>
       <c r="T43">
-        <v>1.524539957758566</v>
+        <v>1.547261574600167</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.114068881017163</v>
+        <v>4.992305336231039</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09813527145563483</v>
+        <v>0.09799156223205857</v>
       </c>
       <c r="C44">
-        <v>175.8856197109046</v>
+        <v>173.5183592687097</v>
       </c>
       <c r="D44">
-        <v>290.0456197109046</v>
+        <v>290.4683592687097</v>
       </c>
       <c r="E44">
-        <v>24.38</v>
+        <v>27.17</v>
       </c>
       <c r="F44">
-        <v>117.18</v>
+        <v>119.97</v>
       </c>
       <c r="G44">
         <v>3.02</v>
@@ -4889,28 +4889,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M44">
-        <v>6.480054</v>
+        <v>6.634341</v>
       </c>
       <c r="N44">
-        <v>25.8703541632653</v>
+        <v>25.7160671632653</v>
       </c>
       <c r="O44">
-        <v>5.432774374285713</v>
+        <v>5.400374104285713</v>
       </c>
       <c r="P44">
-        <v>20.43757978897959</v>
+        <v>20.31569305897959</v>
       </c>
       <c r="Q44">
-        <v>24.10757978897959</v>
+        <v>23.98569305897959</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1375633300959221</v>
+        <v>0.1389581618106291</v>
       </c>
       <c r="T44">
-        <v>1.547261574600167</v>
+        <v>1.570780441155508</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.992305336231041</v>
+        <v>4.876205212132644</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09799156223205857</v>
+        <v>0.09784785300848234</v>
       </c>
       <c r="C45">
-        <v>173.5183592687097</v>
+        <v>171.1523329053529</v>
       </c>
       <c r="D45">
-        <v>290.4683592687097</v>
+        <v>290.8923329053529</v>
       </c>
       <c r="E45">
-        <v>27.17</v>
+        <v>29.96000000000001</v>
       </c>
       <c r="F45">
-        <v>119.97</v>
+        <v>122.76</v>
       </c>
       <c r="G45">
         <v>3.02</v>
@@ -4971,28 +4971,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M45">
-        <v>6.634341</v>
+        <v>6.788628</v>
       </c>
       <c r="N45">
-        <v>25.7160671632653</v>
+        <v>25.5617801632653</v>
       </c>
       <c r="O45">
-        <v>5.400374104285713</v>
+        <v>5.367973834285713</v>
       </c>
       <c r="P45">
-        <v>20.31569305897959</v>
+        <v>20.19380632897959</v>
       </c>
       <c r="Q45">
-        <v>23.98569305897959</v>
+        <v>23.86380632897959</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1389581618106291</v>
+        <v>0.1404028089437184</v>
       </c>
       <c r="T45">
-        <v>1.570780441155508</v>
+        <v>1.595139267230683</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.876205212132644</v>
+        <v>4.765382366402357</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09784785300848234</v>
+        <v>0.09770414378490606</v>
       </c>
       <c r="C46">
-        <v>171.1523329053529</v>
+        <v>168.7875460325947</v>
       </c>
       <c r="D46">
-        <v>290.8923329053529</v>
+        <v>291.3175460325947</v>
       </c>
       <c r="E46">
-        <v>29.96000000000001</v>
+        <v>32.75</v>
       </c>
       <c r="F46">
-        <v>122.76</v>
+        <v>125.55</v>
       </c>
       <c r="G46">
         <v>3.02</v>
@@ -5053,28 +5053,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M46">
-        <v>6.788628</v>
+        <v>6.942915</v>
       </c>
       <c r="N46">
-        <v>25.5617801632653</v>
+        <v>25.4074931632653</v>
       </c>
       <c r="O46">
-        <v>5.367973834285713</v>
+        <v>5.335573564285713</v>
       </c>
       <c r="P46">
-        <v>20.19380632897959</v>
+        <v>20.07191959897959</v>
       </c>
       <c r="Q46">
-        <v>23.86380632897959</v>
+        <v>23.74191959897959</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1404028089437184</v>
+        <v>0.1418999886998292</v>
       </c>
       <c r="T46">
-        <v>1.595139267230683</v>
+        <v>1.620383868799501</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.765382366402357</v>
+        <v>4.659484980482304</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09770414378490606</v>
+        <v>0.09756043456132982</v>
       </c>
       <c r="C47">
-        <v>168.7875460325947</v>
+        <v>166.4240040938842</v>
       </c>
       <c r="D47">
-        <v>291.3175460325947</v>
+        <v>291.7440040938843</v>
       </c>
       <c r="E47">
-        <v>32.75</v>
+        <v>35.54000000000001</v>
       </c>
       <c r="F47">
-        <v>125.55</v>
+        <v>128.34</v>
       </c>
       <c r="G47">
         <v>3.02</v>
@@ -5135,28 +5135,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M47">
-        <v>6.942915</v>
+        <v>7.097202</v>
       </c>
       <c r="N47">
-        <v>25.4074931632653</v>
+        <v>25.2532061632653</v>
       </c>
       <c r="O47">
-        <v>5.335573564285713</v>
+        <v>5.303173294285713</v>
       </c>
       <c r="P47">
-        <v>20.07191959897959</v>
+        <v>19.95003286897959</v>
       </c>
       <c r="Q47">
-        <v>23.74191959897959</v>
+        <v>23.62003286897959</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1418999886998292</v>
+        <v>0.1434526195580182</v>
       </c>
       <c r="T47">
-        <v>1.620383868799501</v>
+        <v>1.646563455611608</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.659484980482304</v>
+        <v>4.558191828732689</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09756043456132982</v>
+        <v>0.09834497533775355</v>
       </c>
       <c r="C48">
-        <v>166.4240040938842</v>
+        <v>161.3209513533679</v>
       </c>
       <c r="D48">
-        <v>291.7440040938843</v>
+        <v>289.430951353368</v>
       </c>
       <c r="E48">
-        <v>35.54000000000001</v>
+        <v>38.33</v>
       </c>
       <c r="F48">
-        <v>128.34</v>
+        <v>131.13</v>
       </c>
       <c r="G48">
         <v>3.02</v>
@@ -5217,45 +5217,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M48">
-        <v>7.097202</v>
+        <v>7.579314</v>
       </c>
       <c r="N48">
-        <v>25.2532061632653</v>
+        <v>24.7710941632653</v>
       </c>
       <c r="O48">
-        <v>5.303173294285713</v>
+        <v>5.201929774285713</v>
       </c>
       <c r="P48">
-        <v>19.95003286897959</v>
+        <v>19.56916438897959</v>
       </c>
       <c r="Q48">
-        <v>23.62003286897959</v>
+        <v>23.23916438897959</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1434526195580182</v>
+        <v>0.1450638402599123</v>
       </c>
       <c r="T48">
-        <v>1.646563455611608</v>
+        <v>1.673730951360021</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.21</v>
       </c>
       <c r="W48">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.558191828732689</v>
+        <v>4.268250156051762</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09834497533775355</v>
+        <v>0.0982210161141773</v>
       </c>
       <c r="C49">
-        <v>161.3209513533679</v>
+        <v>158.8939761378312</v>
       </c>
       <c r="D49">
-        <v>289.430951353368</v>
+        <v>289.7939761378312</v>
       </c>
       <c r="E49">
-        <v>38.33</v>
+        <v>41.12000000000002</v>
       </c>
       <c r="F49">
-        <v>131.13</v>
+        <v>133.92</v>
       </c>
       <c r="G49">
         <v>3.02</v>
@@ -5299,28 +5299,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M49">
-        <v>7.579314</v>
+        <v>7.740576000000002</v>
       </c>
       <c r="N49">
-        <v>24.7710941632653</v>
+        <v>24.6098321632653</v>
       </c>
       <c r="O49">
-        <v>5.201929774285713</v>
+        <v>5.168064754285712</v>
       </c>
       <c r="P49">
-        <v>19.56916438897959</v>
+        <v>19.44176740897959</v>
       </c>
       <c r="Q49">
-        <v>23.23916438897959</v>
+        <v>23.11176740897959</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1450638402599123</v>
+        <v>0.1467370309888025</v>
       </c>
       <c r="T49">
-        <v>1.673730951360021</v>
+        <v>1.701943350791066</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.268250156051762</v>
+        <v>4.179328277800682</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0982210161141773</v>
+        <v>0.09809705689060103</v>
       </c>
       <c r="C50">
-        <v>158.8939761378312</v>
+        <v>156.4679127287042</v>
       </c>
       <c r="D50">
-        <v>289.7939761378312</v>
+        <v>290.1579127287043</v>
       </c>
       <c r="E50">
-        <v>41.11999999999999</v>
+        <v>43.91000000000001</v>
       </c>
       <c r="F50">
-        <v>133.92</v>
+        <v>136.71</v>
       </c>
       <c r="G50">
         <v>3.02</v>
@@ -5381,28 +5381,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M50">
-        <v>7.740576</v>
+        <v>7.901838000000001</v>
       </c>
       <c r="N50">
-        <v>24.6098321632653</v>
+        <v>24.4485701632653</v>
       </c>
       <c r="O50">
-        <v>5.168064754285712</v>
+        <v>5.134199734285713</v>
       </c>
       <c r="P50">
-        <v>19.44176740897959</v>
+        <v>19.31437042897959</v>
       </c>
       <c r="Q50">
-        <v>23.11176740897959</v>
+        <v>22.98437042897959</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1467370309888025</v>
+        <v>0.1484758370403942</v>
       </c>
       <c r="T50">
-        <v>1.701943350791066</v>
+        <v>1.731262118827249</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.179328277800683</v>
+        <v>4.094035863968015</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09809705689060103</v>
+        <v>0.09797309766702476</v>
       </c>
       <c r="C51">
-        <v>156.4679127287042</v>
+        <v>154.0427645655716</v>
       </c>
       <c r="D51">
-        <v>290.1579127287043</v>
+        <v>290.5227645655717</v>
       </c>
       <c r="E51">
-        <v>43.91000000000001</v>
+        <v>46.7</v>
       </c>
       <c r="F51">
-        <v>136.71</v>
+        <v>139.5</v>
       </c>
       <c r="G51">
         <v>3.02</v>
@@ -5463,28 +5463,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M51">
-        <v>7.901838000000001</v>
+        <v>8.0631</v>
       </c>
       <c r="N51">
-        <v>24.4485701632653</v>
+        <v>24.2873081632653</v>
       </c>
       <c r="O51">
-        <v>5.134199734285713</v>
+        <v>5.100334714285713</v>
       </c>
       <c r="P51">
-        <v>19.31437042897959</v>
+        <v>19.18697344897959</v>
       </c>
       <c r="Q51">
-        <v>22.98437042897959</v>
+        <v>22.85697344897959</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1484758370403942</v>
+        <v>0.1502841953340495</v>
       </c>
       <c r="T51">
-        <v>1.731262118827249</v>
+        <v>1.76175363758488</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.094035863968015</v>
+        <v>4.012155146688656</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09797309766702476</v>
+        <v>0.09925928844344852</v>
       </c>
       <c r="C52">
-        <v>154.0427645655716</v>
+        <v>147.5111481588647</v>
       </c>
       <c r="D52">
-        <v>290.5227645655717</v>
+        <v>286.7811481588647</v>
       </c>
       <c r="E52">
-        <v>46.7</v>
+        <v>49.48999999999999</v>
       </c>
       <c r="F52">
-        <v>139.5</v>
+        <v>142.29</v>
       </c>
       <c r="G52">
         <v>3.02</v>
@@ -5545,45 +5545,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M52">
-        <v>8.0631</v>
+        <v>8.722377</v>
       </c>
       <c r="N52">
-        <v>24.2873081632653</v>
+        <v>23.6280311632653</v>
       </c>
       <c r="O52">
-        <v>5.100334714285713</v>
+        <v>4.961886544285712</v>
       </c>
       <c r="P52">
-        <v>19.18697344897959</v>
+        <v>18.66614461897959</v>
       </c>
       <c r="Q52">
-        <v>22.85697344897959</v>
+        <v>22.33614461897959</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1502841953340495</v>
+        <v>0.1521663641703031</v>
       </c>
       <c r="T52">
-        <v>1.76175363758488</v>
+        <v>1.793489708128536</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.21</v>
       </c>
       <c r="W52">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.012155146688656</v>
+        <v>3.708898178015614</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09925928844344852</v>
+        <v>0.09916297921987226</v>
       </c>
       <c r="C53">
-        <v>147.5111481588647</v>
+        <v>144.9979769165133</v>
       </c>
       <c r="D53">
-        <v>286.7811481588647</v>
+        <v>287.0579769165133</v>
       </c>
       <c r="E53">
-        <v>49.48999999999999</v>
+        <v>52.28000000000002</v>
       </c>
       <c r="F53">
-        <v>142.29</v>
+        <v>145.08</v>
       </c>
       <c r="G53">
         <v>3.02</v>
@@ -5627,28 +5627,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M53">
-        <v>8.722377</v>
+        <v>8.893404</v>
       </c>
       <c r="N53">
-        <v>23.6280311632653</v>
+        <v>23.4570041632653</v>
       </c>
       <c r="O53">
-        <v>4.961886544285712</v>
+        <v>4.925970874285713</v>
       </c>
       <c r="P53">
-        <v>18.66614461897959</v>
+        <v>18.53103328897959</v>
       </c>
       <c r="Q53">
-        <v>22.33614461897959</v>
+        <v>22.20103328897959</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1521663641703031</v>
+        <v>0.1541269567080672</v>
       </c>
       <c r="T53">
-        <v>1.793489708128536</v>
+        <v>1.826548114944845</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.708898178015614</v>
+        <v>3.637573213053775</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09916297921987226</v>
+        <v>0.09906666999629599</v>
       </c>
       <c r="C54">
-        <v>144.9979769165133</v>
+        <v>142.4853406340623</v>
       </c>
       <c r="D54">
-        <v>287.0579769165133</v>
+        <v>287.3353406340623</v>
       </c>
       <c r="E54">
-        <v>52.28000000000002</v>
+        <v>55.07000000000001</v>
       </c>
       <c r="F54">
-        <v>145.08</v>
+        <v>147.87</v>
       </c>
       <c r="G54">
         <v>3.02</v>
@@ -5709,28 +5709,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M54">
-        <v>8.893404</v>
+        <v>9.064431000000001</v>
       </c>
       <c r="N54">
-        <v>23.4570041632653</v>
+        <v>23.2859771632653</v>
       </c>
       <c r="O54">
-        <v>4.925970874285713</v>
+        <v>4.890055204285713</v>
       </c>
       <c r="P54">
-        <v>18.53103328897959</v>
+        <v>18.39592195897959</v>
       </c>
       <c r="Q54">
-        <v>22.20103328897959</v>
+        <v>22.06592195897959</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1541269567080672</v>
+        <v>0.1561709787155234</v>
       </c>
       <c r="T54">
-        <v>1.826548114944845</v>
+        <v>1.861013262476741</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.637573213053775</v>
+        <v>3.568939756203704</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09906666999629599</v>
+        <v>0.09897036077271973</v>
       </c>
       <c r="C55">
-        <v>142.4853406340623</v>
+        <v>139.9732408636923</v>
       </c>
       <c r="D55">
-        <v>287.3353406340623</v>
+        <v>287.6132408636923</v>
       </c>
       <c r="E55">
-        <v>55.07000000000001</v>
+        <v>57.86</v>
       </c>
       <c r="F55">
-        <v>147.87</v>
+        <v>150.66</v>
       </c>
       <c r="G55">
         <v>3.02</v>
@@ -5791,28 +5791,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M55">
-        <v>9.064431000000001</v>
+        <v>9.235458</v>
       </c>
       <c r="N55">
-        <v>23.2859771632653</v>
+        <v>23.1149501632653</v>
       </c>
       <c r="O55">
-        <v>4.890055204285713</v>
+        <v>4.854139534285713</v>
       </c>
       <c r="P55">
-        <v>18.39592195897959</v>
+        <v>18.26081062897958</v>
       </c>
       <c r="Q55">
-        <v>22.06592195897959</v>
+        <v>21.93081062897959</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1561709787155234</v>
+        <v>0.1583038712450429</v>
       </c>
       <c r="T55">
-        <v>1.861013262476741</v>
+        <v>1.896976894683938</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.568939756203704</v>
+        <v>3.502848279236969</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09897036077271973</v>
+        <v>0.1000906515491435</v>
       </c>
       <c r="C56">
-        <v>139.9732408636923</v>
+        <v>133.9835135632775</v>
       </c>
       <c r="D56">
-        <v>287.6132408636923</v>
+        <v>284.4135135632775</v>
       </c>
       <c r="E56">
-        <v>57.86</v>
+        <v>60.65000000000002</v>
       </c>
       <c r="F56">
-        <v>150.66</v>
+        <v>153.45</v>
       </c>
       <c r="G56">
         <v>3.02</v>
@@ -5873,45 +5873,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M56">
-        <v>9.235458</v>
+        <v>9.836145000000002</v>
       </c>
       <c r="N56">
-        <v>23.1149501632653</v>
+        <v>22.5142631632653</v>
       </c>
       <c r="O56">
-        <v>4.854139534285713</v>
+        <v>4.727995264285712</v>
       </c>
       <c r="P56">
-        <v>18.26081062897958</v>
+        <v>17.78626789897958</v>
       </c>
       <c r="Q56">
-        <v>21.93081062897959</v>
+        <v>21.45626789897958</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1583038712450429</v>
+        <v>0.1605315589980966</v>
       </c>
       <c r="T56">
-        <v>1.896976894683938</v>
+        <v>1.934538910544787</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.21</v>
       </c>
       <c r="W56">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.502848279236969</v>
+        <v>3.288931605142593</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1000906515491435</v>
+        <v>0.1000164623255672</v>
       </c>
       <c r="C57">
-        <v>133.9835135632775</v>
+        <v>131.4032068197054</v>
       </c>
       <c r="D57">
-        <v>284.4135135632775</v>
+        <v>284.6232068197054</v>
       </c>
       <c r="E57">
-        <v>60.65000000000002</v>
+        <v>63.44000000000001</v>
       </c>
       <c r="F57">
-        <v>153.45</v>
+        <v>156.24</v>
       </c>
       <c r="G57">
         <v>3.02</v>
@@ -5955,28 +5955,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M57">
-        <v>9.836145000000002</v>
+        <v>10.014984</v>
       </c>
       <c r="N57">
-        <v>22.5142631632653</v>
+        <v>22.3354241632653</v>
       </c>
       <c r="O57">
-        <v>4.727995264285712</v>
+        <v>4.690439074285712</v>
       </c>
       <c r="P57">
-        <v>17.78626789897958</v>
+        <v>17.64498508897958</v>
       </c>
       <c r="Q57">
-        <v>21.45626789897958</v>
+        <v>21.31498508897958</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1605315589980966</v>
+        <v>0.16286050528538</v>
       </c>
       <c r="T57">
-        <v>1.934538910544787</v>
+        <v>1.973808290762948</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.288931605142593</v>
+        <v>3.23020068362219</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1000164623255672</v>
+        <v>0.09994227310199096</v>
       </c>
       <c r="C58">
-        <v>131.4032068197054</v>
+        <v>128.8232095108323</v>
       </c>
       <c r="D58">
-        <v>284.6232068197054</v>
+        <v>284.8332095108324</v>
       </c>
       <c r="E58">
-        <v>63.44000000000001</v>
+        <v>66.23000000000003</v>
       </c>
       <c r="F58">
-        <v>156.24</v>
+        <v>159.03</v>
       </c>
       <c r="G58">
         <v>3.02</v>
@@ -6037,28 +6037,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M58">
-        <v>10.014984</v>
+        <v>10.193823</v>
       </c>
       <c r="N58">
-        <v>22.3354241632653</v>
+        <v>22.1565851632653</v>
       </c>
       <c r="O58">
-        <v>4.690439074285712</v>
+        <v>4.652882884285712</v>
       </c>
       <c r="P58">
-        <v>17.64498508897958</v>
+        <v>17.50370227897958</v>
       </c>
       <c r="Q58">
-        <v>21.31498508897958</v>
+        <v>21.17370227897958</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.16286050528538</v>
+        <v>0.1652977746557929</v>
       </c>
       <c r="T58">
-        <v>1.973808290762948</v>
+        <v>2.014904153781954</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.23020068362219</v>
+        <v>3.173530496190222</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09994227310199096</v>
+        <v>0.0998680838784147</v>
       </c>
       <c r="C59">
-        <v>128.8232095108323</v>
+        <v>126.2435223220917</v>
       </c>
       <c r="D59">
-        <v>284.8332095108324</v>
+        <v>285.0435223220917</v>
       </c>
       <c r="E59">
-        <v>66.23000000000003</v>
+        <v>69.02000000000002</v>
       </c>
       <c r="F59">
-        <v>159.03</v>
+        <v>161.82</v>
       </c>
       <c r="G59">
         <v>3.02</v>
@@ -6119,28 +6119,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M59">
-        <v>10.193823</v>
+        <v>10.372662</v>
       </c>
       <c r="N59">
-        <v>22.1565851632653</v>
+        <v>21.9777461632653</v>
       </c>
       <c r="O59">
-        <v>4.652882884285712</v>
+        <v>4.615326694285712</v>
       </c>
       <c r="P59">
-        <v>17.50370227897958</v>
+        <v>17.36241946897958</v>
       </c>
       <c r="Q59">
-        <v>21.17370227897958</v>
+        <v>21.03241946897958</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1652977746557929</v>
+        <v>0.1678511044724159</v>
       </c>
       <c r="T59">
-        <v>2.014904153781954</v>
+        <v>2.057956962659007</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.173530496190222</v>
+        <v>3.118814453152459</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09986808387841468</v>
+        <v>0.09979389465483843</v>
       </c>
       <c r="C60">
-        <v>126.2435223220918</v>
+        <v>123.6641459409433</v>
       </c>
       <c r="D60">
-        <v>285.0435223220919</v>
+        <v>285.2541459409433</v>
       </c>
       <c r="E60">
-        <v>69.02</v>
+        <v>71.80999999999999</v>
       </c>
       <c r="F60">
-        <v>161.82</v>
+        <v>164.61</v>
       </c>
       <c r="G60">
         <v>3.02</v>
@@ -6201,28 +6201,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M60">
-        <v>10.372662</v>
+        <v>10.551501</v>
       </c>
       <c r="N60">
-        <v>21.9777461632653</v>
+        <v>21.7989071632653</v>
       </c>
       <c r="O60">
-        <v>4.615326694285713</v>
+        <v>4.577770504285712</v>
       </c>
       <c r="P60">
-        <v>17.36241946897959</v>
+        <v>17.22113665897959</v>
       </c>
       <c r="Q60">
-        <v>21.03241946897959</v>
+        <v>20.89113665897958</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1678511044724159</v>
+        <v>0.1705289869630205</v>
       </c>
       <c r="T60">
-        <v>2.057956962659007</v>
+        <v>2.103109908554453</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.11881445315246</v>
+        <v>3.065953191234621</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09979389465483843</v>
+        <v>0.09971970543126217</v>
       </c>
       <c r="C61">
-        <v>123.6641459409433</v>
+        <v>121.0850810568797</v>
       </c>
       <c r="D61">
-        <v>285.2541459409433</v>
+        <v>285.4650810568797</v>
       </c>
       <c r="E61">
-        <v>71.80999999999999</v>
+        <v>74.60000000000001</v>
       </c>
       <c r="F61">
-        <v>164.61</v>
+        <v>167.4</v>
       </c>
       <c r="G61">
         <v>3.02</v>
@@ -6283,28 +6283,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M61">
-        <v>10.551501</v>
+        <v>10.73034</v>
       </c>
       <c r="N61">
-        <v>21.7989071632653</v>
+        <v>21.6200681632653</v>
       </c>
       <c r="O61">
-        <v>4.577770504285712</v>
+        <v>4.540214314285713</v>
       </c>
       <c r="P61">
-        <v>17.22113665897959</v>
+        <v>17.07985384897959</v>
       </c>
       <c r="Q61">
-        <v>20.89113665897958</v>
+        <v>20.74985384897958</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1705289869630205</v>
+        <v>0.1733407635781554</v>
       </c>
       <c r="T61">
-        <v>2.103109908554453</v>
+        <v>2.150520501744671</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.065953191234621</v>
+        <v>3.014853971380711</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09971970543126217</v>
+        <v>0.1034043362076859</v>
       </c>
       <c r="C62">
-        <v>121.0850810568797</v>
+        <v>108.1825656236844</v>
       </c>
       <c r="D62">
-        <v>285.4650810568797</v>
+        <v>275.3525656236844</v>
       </c>
       <c r="E62">
-        <v>74.60000000000001</v>
+        <v>77.39</v>
       </c>
       <c r="F62">
-        <v>167.4</v>
+        <v>170.19</v>
       </c>
       <c r="G62">
         <v>3.02</v>
@@ -6365,45 +6365,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M62">
-        <v>10.73034</v>
+        <v>12.236661</v>
       </c>
       <c r="N62">
-        <v>21.6200681632653</v>
+        <v>20.1137471632653</v>
       </c>
       <c r="O62">
-        <v>4.540214314285713</v>
+        <v>4.223886904285712</v>
       </c>
       <c r="P62">
-        <v>17.07985384897959</v>
+        <v>15.88986025897958</v>
       </c>
       <c r="Q62">
-        <v>20.74985384897958</v>
+        <v>19.55986025897958</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1733407635781554</v>
+        <v>0.1762967338658613</v>
       </c>
       <c r="T62">
-        <v>2.150520501744671</v>
+        <v>2.200362407406183</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.21</v>
       </c>
       <c r="W62">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.014853971380711</v>
+        <v>2.643728396436356</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1034043362076859</v>
+        <v>0.1033917669841097</v>
       </c>
       <c r="C63">
-        <v>108.1825656236844</v>
+        <v>105.4258440126669</v>
       </c>
       <c r="D63">
-        <v>275.3525656236844</v>
+        <v>275.3858440126669</v>
       </c>
       <c r="E63">
-        <v>77.39</v>
+        <v>80.17999999999999</v>
       </c>
       <c r="F63">
-        <v>170.19</v>
+        <v>172.98</v>
       </c>
       <c r="G63">
         <v>3.02</v>
@@ -6447,28 +6447,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M63">
-        <v>12.236661</v>
+        <v>12.437262</v>
       </c>
       <c r="N63">
-        <v>20.1137471632653</v>
+        <v>19.9131461632653</v>
       </c>
       <c r="O63">
-        <v>4.223886904285712</v>
+        <v>4.181760694285713</v>
       </c>
       <c r="P63">
-        <v>15.88986025897958</v>
+        <v>15.73138546897959</v>
       </c>
       <c r="Q63">
-        <v>19.55986025897958</v>
+        <v>19.40138546897958</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1762967338658613</v>
+        <v>0.1794082815371307</v>
       </c>
       <c r="T63">
-        <v>2.200362407406183</v>
+        <v>2.252827571260406</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.643728396436356</v>
+        <v>2.601087615848673</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1033917669841097</v>
+        <v>0.1033791977605334</v>
       </c>
       <c r="C64">
-        <v>105.4258440126669</v>
+        <v>102.6691304464993</v>
       </c>
       <c r="D64">
-        <v>275.3858440126669</v>
+        <v>275.4191304464994</v>
       </c>
       <c r="E64">
-        <v>80.17999999999999</v>
+        <v>82.97000000000001</v>
       </c>
       <c r="F64">
-        <v>172.98</v>
+        <v>175.77</v>
       </c>
       <c r="G64">
         <v>3.02</v>
@@ -6529,28 +6529,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M64">
-        <v>12.437262</v>
+        <v>12.637863</v>
       </c>
       <c r="N64">
-        <v>19.9131461632653</v>
+        <v>19.7125451632653</v>
       </c>
       <c r="O64">
-        <v>4.181760694285713</v>
+        <v>4.139634484285712</v>
       </c>
       <c r="P64">
-        <v>15.73138546897959</v>
+        <v>15.57291067897959</v>
       </c>
       <c r="Q64">
-        <v>19.40138546897958</v>
+        <v>19.24291067897958</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1794082815371307</v>
+        <v>0.1826880209744146</v>
       </c>
       <c r="T64">
-        <v>2.252827571260406</v>
+        <v>2.30812868991756</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.601087615848673</v>
+        <v>2.559800510835202</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1033791977605334</v>
+        <v>0.1033666285369571</v>
       </c>
       <c r="C65">
-        <v>102.6691304464993</v>
+        <v>99.9124249280992</v>
       </c>
       <c r="D65">
-        <v>275.4191304464994</v>
+        <v>275.4524249280992</v>
       </c>
       <c r="E65">
-        <v>82.97000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F65">
-        <v>175.77</v>
+        <v>178.56</v>
       </c>
       <c r="G65">
         <v>3.02</v>
@@ -6611,28 +6611,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M65">
-        <v>12.637863</v>
+        <v>12.838464</v>
       </c>
       <c r="N65">
-        <v>19.7125451632653</v>
+        <v>19.5119441632653</v>
       </c>
       <c r="O65">
-        <v>4.139634484285712</v>
+        <v>4.097508274285713</v>
       </c>
       <c r="P65">
-        <v>15.57291067897959</v>
+        <v>15.41443588897959</v>
       </c>
       <c r="Q65">
-        <v>19.24291067897958</v>
+        <v>19.08443588897958</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1826880209744146</v>
+        <v>0.1861499681582143</v>
       </c>
       <c r="T65">
-        <v>2.30812868991756</v>
+        <v>2.366502092944556</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.559800510835202</v>
+        <v>2.519803627853402</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1033666285369571</v>
+        <v>0.1053567093133809</v>
       </c>
       <c r="C66">
-        <v>99.9124249280992</v>
+        <v>91.94929735121022</v>
       </c>
       <c r="D66">
-        <v>275.4524249280992</v>
+        <v>270.2792973512102</v>
       </c>
       <c r="E66">
-        <v>85.76000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="F66">
-        <v>178.56</v>
+        <v>181.35</v>
       </c>
       <c r="G66">
         <v>3.02</v>
@@ -6693,45 +6693,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M66">
-        <v>12.838464</v>
+        <v>13.74633</v>
       </c>
       <c r="N66">
-        <v>19.5119441632653</v>
+        <v>18.6040781632653</v>
       </c>
       <c r="O66">
-        <v>4.097508274285713</v>
+        <v>3.906856414285713</v>
       </c>
       <c r="P66">
-        <v>15.41443588897959</v>
+        <v>14.69722174897959</v>
       </c>
       <c r="Q66">
-        <v>19.08443588897958</v>
+        <v>18.36722174897959</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1861499681582143</v>
+        <v>0.1898097408953739</v>
       </c>
       <c r="T66">
-        <v>2.366502092944556</v>
+        <v>2.428211119001666</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.21</v>
       </c>
       <c r="W66">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.519803627853402</v>
+        <v>2.35338509720524</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1053567093133809</v>
+        <v>0.1053749500898046</v>
       </c>
       <c r="C67">
-        <v>91.94929735121022</v>
+        <v>89.11277975835745</v>
       </c>
       <c r="D67">
-        <v>270.2792973512102</v>
+        <v>270.2327797583575</v>
       </c>
       <c r="E67">
-        <v>88.55</v>
+        <v>91.34000000000002</v>
       </c>
       <c r="F67">
-        <v>181.35</v>
+        <v>184.14</v>
       </c>
       <c r="G67">
         <v>3.02</v>
@@ -6775,28 +6775,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M67">
-        <v>13.74633</v>
+        <v>13.957812</v>
       </c>
       <c r="N67">
-        <v>18.6040781632653</v>
+        <v>18.3925961632653</v>
       </c>
       <c r="O67">
-        <v>3.906856414285713</v>
+        <v>3.862445194285712</v>
       </c>
       <c r="P67">
-        <v>14.69722174897959</v>
+        <v>14.53015096897958</v>
       </c>
       <c r="Q67">
-        <v>18.36722174897959</v>
+        <v>18.20015096897959</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1898097408953739</v>
+        <v>0.1936847943817783</v>
       </c>
       <c r="T67">
-        <v>2.428211119001666</v>
+        <v>2.493550087768018</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.35338509720524</v>
+        <v>2.317727747247584</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1053749500898046</v>
+        <v>0.1053931908662284</v>
       </c>
       <c r="C68">
-        <v>89.11277975835745</v>
+        <v>86.27627817497421</v>
       </c>
       <c r="D68">
-        <v>270.2327797583575</v>
+        <v>270.1862781749742</v>
       </c>
       <c r="E68">
-        <v>91.34000000000002</v>
+        <v>94.13000000000001</v>
       </c>
       <c r="F68">
-        <v>184.14</v>
+        <v>186.93</v>
       </c>
       <c r="G68">
         <v>3.02</v>
@@ -6857,28 +6857,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M68">
-        <v>13.957812</v>
+        <v>14.169294</v>
       </c>
       <c r="N68">
-        <v>18.3925961632653</v>
+        <v>18.1811141632653</v>
       </c>
       <c r="O68">
-        <v>3.862445194285712</v>
+        <v>3.818033974285713</v>
       </c>
       <c r="P68">
-        <v>14.53015096897958</v>
+        <v>14.36308018897959</v>
       </c>
       <c r="Q68">
-        <v>18.20015096897959</v>
+        <v>18.03308018897959</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1936847943817783</v>
+        <v>0.1977946995946314</v>
       </c>
       <c r="T68">
-        <v>2.493550087768018</v>
+        <v>2.56284899403536</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.317727747247584</v>
+        <v>2.283134795796128</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1053931908662284</v>
+        <v>0.1054114316426521</v>
       </c>
       <c r="C69">
-        <v>86.27627817497421</v>
+        <v>83.43979259279712</v>
       </c>
       <c r="D69">
-        <v>270.1862781749742</v>
+        <v>270.1397925927972</v>
       </c>
       <c r="E69">
-        <v>94.13000000000001</v>
+        <v>96.92000000000003</v>
       </c>
       <c r="F69">
-        <v>186.93</v>
+        <v>189.72</v>
       </c>
       <c r="G69">
         <v>3.02</v>
@@ -6939,28 +6939,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M69">
-        <v>14.169294</v>
+        <v>14.380776</v>
       </c>
       <c r="N69">
-        <v>18.1811141632653</v>
+        <v>17.9696321632653</v>
       </c>
       <c r="O69">
-        <v>3.818033974285713</v>
+        <v>3.773622754285712</v>
       </c>
       <c r="P69">
-        <v>14.36308018897959</v>
+        <v>14.19600940897958</v>
       </c>
       <c r="Q69">
-        <v>18.03308018897959</v>
+        <v>17.86600940897959</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1977946995946314</v>
+        <v>0.2021614738832878</v>
       </c>
       <c r="T69">
-        <v>2.56284899403536</v>
+        <v>2.636479081944412</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.283134795796128</v>
+        <v>2.249559284093243</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1054114316426521</v>
+        <v>0.1054296724190758</v>
       </c>
       <c r="C70">
-        <v>83.43979259279712</v>
+        <v>80.6033230035687</v>
       </c>
       <c r="D70">
-        <v>270.1397925927972</v>
+        <v>270.0933230035687</v>
       </c>
       <c r="E70">
-        <v>96.92000000000003</v>
+        <v>99.71000000000002</v>
       </c>
       <c r="F70">
-        <v>189.72</v>
+        <v>192.51</v>
       </c>
       <c r="G70">
         <v>3.02</v>
@@ -7021,28 +7021,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M70">
-        <v>14.380776</v>
+        <v>14.592258</v>
       </c>
       <c r="N70">
-        <v>17.9696321632653</v>
+        <v>17.7581501632653</v>
       </c>
       <c r="O70">
-        <v>3.773622754285712</v>
+        <v>3.729211534285712</v>
       </c>
       <c r="P70">
-        <v>14.19600940897958</v>
+        <v>14.02893862897959</v>
       </c>
       <c r="Q70">
-        <v>17.86600940897959</v>
+        <v>17.69893862897959</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2021614738832878</v>
+        <v>0.2068099755454059</v>
       </c>
       <c r="T70">
-        <v>2.636479081944412</v>
+        <v>2.71485949810566</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.249559284093243</v>
+        <v>2.216956975628124</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1054296724190758</v>
+        <v>0.1054479131954996</v>
       </c>
       <c r="C71">
-        <v>80.6033230035687</v>
+        <v>77.76686939903692</v>
       </c>
       <c r="D71">
-        <v>270.0933230035687</v>
+        <v>270.046869399037</v>
       </c>
       <c r="E71">
-        <v>99.71000000000002</v>
+        <v>102.5</v>
       </c>
       <c r="F71">
-        <v>192.51</v>
+        <v>195.3</v>
       </c>
       <c r="G71">
         <v>3.02</v>
@@ -7103,28 +7103,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M71">
-        <v>14.592258</v>
+        <v>14.80374</v>
       </c>
       <c r="N71">
-        <v>17.7581501632653</v>
+        <v>17.5466681632653</v>
       </c>
       <c r="O71">
-        <v>3.729211534285712</v>
+        <v>3.684800314285713</v>
       </c>
       <c r="P71">
-        <v>14.02893862897959</v>
+        <v>13.86186784897959</v>
       </c>
       <c r="Q71">
-        <v>17.69893862897959</v>
+        <v>17.53186784897959</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2068099755454059</v>
+        <v>0.211768377318332</v>
       </c>
       <c r="T71">
-        <v>2.71485949810566</v>
+        <v>2.798465275344325</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.216956975628124</v>
+        <v>2.18528616169058</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1054479131954996</v>
+        <v>0.1054661539719233</v>
       </c>
       <c r="C72">
-        <v>77.76686939903692</v>
+        <v>74.93043177095552</v>
       </c>
       <c r="D72">
-        <v>270.046869399037</v>
+        <v>270.0004317709556</v>
       </c>
       <c r="E72">
-        <v>102.5</v>
+        <v>105.29</v>
       </c>
       <c r="F72">
-        <v>195.3</v>
+        <v>198.09</v>
       </c>
       <c r="G72">
         <v>3.02</v>
@@ -7185,28 +7185,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M72">
-        <v>14.80374</v>
+        <v>15.015222</v>
       </c>
       <c r="N72">
-        <v>17.5466681632653</v>
+        <v>17.3351861632653</v>
       </c>
       <c r="O72">
-        <v>3.684800314285713</v>
+        <v>3.640389094285712</v>
       </c>
       <c r="P72">
-        <v>13.86186784897959</v>
+        <v>13.69479706897959</v>
       </c>
       <c r="Q72">
-        <v>17.53186784897959</v>
+        <v>17.36479706897958</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.211768377318332</v>
+        <v>0.2170687378342184</v>
       </c>
       <c r="T72">
-        <v>2.798465275344325</v>
+        <v>2.887836968254623</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.18528616169058</v>
+        <v>2.154507483356909</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1054661539719233</v>
+        <v>0.1054843947483471</v>
       </c>
       <c r="C73">
-        <v>74.93043177095555</v>
+        <v>72.09401011108412</v>
       </c>
       <c r="D73">
-        <v>270.0004317709556</v>
+        <v>269.9540101110841</v>
       </c>
       <c r="E73">
-        <v>105.29</v>
+        <v>108.08</v>
       </c>
       <c r="F73">
-        <v>198.09</v>
+        <v>200.88</v>
       </c>
       <c r="G73">
         <v>3.02</v>
@@ -7267,28 +7267,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M73">
-        <v>15.015222</v>
+        <v>15.226704</v>
       </c>
       <c r="N73">
-        <v>17.3351861632653</v>
+        <v>17.1237041632653</v>
       </c>
       <c r="O73">
-        <v>3.640389094285712</v>
+        <v>3.595977874285713</v>
       </c>
       <c r="P73">
-        <v>13.69479706897959</v>
+        <v>13.52772628897959</v>
       </c>
       <c r="Q73">
-        <v>17.36479706897958</v>
+        <v>17.19772628897959</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2170687378342183</v>
+        <v>0.2227476955298109</v>
       </c>
       <c r="T73">
-        <v>2.887836968254621</v>
+        <v>2.983592353515654</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.154507483356909</v>
+        <v>2.124583768310286</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1054843947483471</v>
+        <v>0.1055026355247708</v>
       </c>
       <c r="C74">
-        <v>72.09401011108412</v>
+        <v>69.25760441118754</v>
       </c>
       <c r="D74">
-        <v>269.9540101110841</v>
+        <v>269.9076044111875</v>
       </c>
       <c r="E74">
-        <v>108.08</v>
+        <v>110.87</v>
       </c>
       <c r="F74">
-        <v>200.88</v>
+        <v>203.67</v>
       </c>
       <c r="G74">
         <v>3.02</v>
@@ -7349,28 +7349,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M74">
-        <v>15.226704</v>
+        <v>15.438186</v>
       </c>
       <c r="N74">
-        <v>17.1237041632653</v>
+        <v>16.9122221632653</v>
       </c>
       <c r="O74">
-        <v>3.595977874285713</v>
+        <v>3.551566654285712</v>
       </c>
       <c r="P74">
-        <v>13.52772628897959</v>
+        <v>13.36065550897959</v>
       </c>
       <c r="Q74">
-        <v>17.19772628897959</v>
+        <v>17.03065550897959</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2227476955298109</v>
+        <v>0.2288473167584104</v>
       </c>
       <c r="T74">
-        <v>2.983592353515654</v>
+        <v>3.086440730277503</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.124583768310286</v>
+        <v>2.095479881073159</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1055026355247708</v>
+        <v>0.1055208763011946</v>
       </c>
       <c r="C75">
-        <v>69.25760441118754</v>
+        <v>66.42121466303658</v>
       </c>
       <c r="D75">
-        <v>269.9076044111875</v>
+        <v>269.8612146630366</v>
       </c>
       <c r="E75">
-        <v>110.87</v>
+        <v>113.66</v>
       </c>
       <c r="F75">
-        <v>203.67</v>
+        <v>206.46</v>
       </c>
       <c r="G75">
         <v>3.02</v>
@@ -7431,28 +7431,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M75">
-        <v>15.438186</v>
+        <v>15.649668</v>
       </c>
       <c r="N75">
-        <v>16.9122221632653</v>
+        <v>16.7007401632653</v>
       </c>
       <c r="O75">
-        <v>3.551566654285712</v>
+        <v>3.507155434285712</v>
       </c>
       <c r="P75">
-        <v>13.36065550897959</v>
+        <v>13.19358472897959</v>
       </c>
       <c r="Q75">
-        <v>17.03065550897959</v>
+        <v>16.86358472897959</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2288473167584104</v>
+        <v>0.235416139619979</v>
       </c>
       <c r="T75">
-        <v>3.086440730277503</v>
+        <v>3.197200520636419</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.095479881073159</v>
+        <v>2.06716258538298</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1055208763011946</v>
+        <v>0.1055391170776183</v>
       </c>
       <c r="C76">
-        <v>66.42121466303658</v>
+        <v>63.58484085840774</v>
       </c>
       <c r="D76">
-        <v>269.8612146630366</v>
+        <v>269.8148408584078</v>
       </c>
       <c r="E76">
-        <v>113.66</v>
+        <v>116.45</v>
       </c>
       <c r="F76">
-        <v>206.46</v>
+        <v>209.25</v>
       </c>
       <c r="G76">
         <v>3.02</v>
@@ -7513,28 +7513,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M76">
-        <v>15.649668</v>
+        <v>15.86115</v>
       </c>
       <c r="N76">
-        <v>16.7007401632653</v>
+        <v>16.4892581632653</v>
       </c>
       <c r="O76">
-        <v>3.507155434285712</v>
+        <v>3.462744214285713</v>
       </c>
       <c r="P76">
-        <v>13.19358472897959</v>
+        <v>13.02651394897958</v>
       </c>
       <c r="Q76">
-        <v>16.86358472897959</v>
+        <v>16.69651394897959</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.235416139619979</v>
+        <v>0.2425104683104732</v>
       </c>
       <c r="T76">
-        <v>3.197200520636419</v>
+        <v>3.316821094224047</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.06716258538298</v>
+        <v>2.039600417577874</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1055391170776183</v>
+        <v>0.105557357854042</v>
       </c>
       <c r="C77">
-        <v>63.58484085840774</v>
+        <v>60.7484829890831</v>
       </c>
       <c r="D77">
-        <v>269.8148408584078</v>
+        <v>269.7684829890831</v>
       </c>
       <c r="E77">
-        <v>116.45</v>
+        <v>119.24</v>
       </c>
       <c r="F77">
-        <v>209.25</v>
+        <v>212.04</v>
       </c>
       <c r="G77">
         <v>3.02</v>
@@ -7595,28 +7595,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M77">
-        <v>15.86115</v>
+        <v>16.072632</v>
       </c>
       <c r="N77">
-        <v>16.4892581632653</v>
+        <v>16.2777761632653</v>
       </c>
       <c r="O77">
-        <v>3.462744214285713</v>
+        <v>3.418332994285712</v>
       </c>
       <c r="P77">
-        <v>13.02651394897958</v>
+        <v>12.85944316897958</v>
       </c>
       <c r="Q77">
-        <v>16.69651394897959</v>
+        <v>16.52944316897958</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2425104683104732</v>
+        <v>0.2501959910585084</v>
       </c>
       <c r="T77">
-        <v>3.316821094224047</v>
+        <v>3.446410048943978</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.039600417577874</v>
+        <v>2.012763569978165</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.105557357854042</v>
+        <v>0.1142134586304658</v>
       </c>
       <c r="C78">
-        <v>60.7484829890831</v>
+        <v>37.62143982318949</v>
       </c>
       <c r="D78">
-        <v>269.7684829890831</v>
+        <v>249.4314398231895</v>
       </c>
       <c r="E78">
-        <v>119.24</v>
+        <v>122.03</v>
       </c>
       <c r="F78">
-        <v>212.04</v>
+        <v>214.83</v>
       </c>
       <c r="G78">
         <v>3.02</v>
@@ -7677,45 +7677,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M78">
-        <v>16.072632</v>
+        <v>19.3347</v>
       </c>
       <c r="N78">
-        <v>16.2777761632653</v>
+        <v>13.0157081632653</v>
       </c>
       <c r="O78">
-        <v>3.418332994285712</v>
+        <v>2.733298714285712</v>
       </c>
       <c r="P78">
-        <v>12.85944316897958</v>
+        <v>10.28240944897959</v>
       </c>
       <c r="Q78">
-        <v>16.52944316897958</v>
+        <v>13.95240944897959</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2501959910585084</v>
+        <v>0.2585498201324599</v>
       </c>
       <c r="T78">
-        <v>3.446410048943978</v>
+        <v>3.587267608422164</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.21</v>
       </c>
       <c r="W78">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.012763569978165</v>
+        <v>1.673178697536827</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1142134586304658</v>
+        <v>0.1143438794068895</v>
       </c>
       <c r="C79">
-        <v>37.62143982318949</v>
+        <v>34.54844450014377</v>
       </c>
       <c r="D79">
-        <v>249.4314398231895</v>
+        <v>249.1484445001438</v>
       </c>
       <c r="E79">
-        <v>122.03</v>
+        <v>124.82</v>
       </c>
       <c r="F79">
-        <v>214.83</v>
+        <v>217.62</v>
       </c>
       <c r="G79">
         <v>3.02</v>
@@ -7759,28 +7759,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M79">
-        <v>19.3347</v>
+        <v>19.5858</v>
       </c>
       <c r="N79">
-        <v>13.0157081632653</v>
+        <v>12.7646081632653</v>
       </c>
       <c r="O79">
-        <v>2.733298714285712</v>
+        <v>2.680567714285713</v>
       </c>
       <c r="P79">
-        <v>10.28240944897959</v>
+        <v>10.08404044897959</v>
       </c>
       <c r="Q79">
-        <v>13.95240944897959</v>
+        <v>13.75404044897959</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2585498201324599</v>
+        <v>0.2676630882131341</v>
       </c>
       <c r="T79">
-        <v>3.587267608422164</v>
+        <v>3.740930400580184</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.673178697536827</v>
+        <v>1.651727688594048</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1143438794068895</v>
+        <v>0.1144743001833132</v>
       </c>
       <c r="C80">
-        <v>34.54844450014377</v>
+        <v>31.47609060059301</v>
       </c>
       <c r="D80">
-        <v>249.1484445001438</v>
+        <v>248.866090600593</v>
       </c>
       <c r="E80">
-        <v>124.82</v>
+        <v>127.61</v>
       </c>
       <c r="F80">
-        <v>217.62</v>
+        <v>220.41</v>
       </c>
       <c r="G80">
         <v>3.02</v>
@@ -7841,28 +7841,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M80">
-        <v>19.5858</v>
+        <v>19.8369</v>
       </c>
       <c r="N80">
-        <v>12.7646081632653</v>
+        <v>12.5135081632653</v>
       </c>
       <c r="O80">
-        <v>2.680567714285713</v>
+        <v>2.627836714285713</v>
       </c>
       <c r="P80">
-        <v>10.08404044897959</v>
+        <v>9.885671448979586</v>
       </c>
       <c r="Q80">
-        <v>13.75404044897959</v>
+        <v>13.55567144897959</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2676630882131341</v>
+        <v>0.277644286587206</v>
       </c>
       <c r="T80">
-        <v>3.740930400580184</v>
+        <v>3.909227744372302</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.651727688594048</v>
+        <v>1.630819743168807</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1144743001833132</v>
+        <v>0.114604720959737</v>
       </c>
       <c r="C81">
-        <v>31.47609060059301</v>
+        <v>28.40437594627656</v>
       </c>
       <c r="D81">
-        <v>248.866090600593</v>
+        <v>248.5843759462766</v>
       </c>
       <c r="E81">
-        <v>127.61</v>
+        <v>130.4</v>
       </c>
       <c r="F81">
-        <v>220.41</v>
+        <v>223.2</v>
       </c>
       <c r="G81">
         <v>3.02</v>
@@ -7923,28 +7923,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M81">
-        <v>19.8369</v>
+        <v>20.088</v>
       </c>
       <c r="N81">
-        <v>12.5135081632653</v>
+        <v>12.2624081632653</v>
       </c>
       <c r="O81">
-        <v>2.627836714285713</v>
+        <v>2.575105714285713</v>
       </c>
       <c r="P81">
-        <v>9.885671448979586</v>
+        <v>9.687302448979587</v>
       </c>
       <c r="Q81">
-        <v>13.55567144897959</v>
+        <v>13.35730244897959</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.277644286587206</v>
+        <v>0.288623604798685</v>
       </c>
       <c r="T81">
-        <v>3.909227744372302</v>
+        <v>4.094354822543632</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.630819743168807</v>
+        <v>1.610434496379197</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.114604720959737</v>
+        <v>0.1147351417361607</v>
       </c>
       <c r="C82">
-        <v>28.40437594627656</v>
+        <v>25.33329836878593</v>
       </c>
       <c r="D82">
-        <v>248.5843759462766</v>
+        <v>248.3032983687859</v>
       </c>
       <c r="E82">
-        <v>130.4</v>
+        <v>133.19</v>
       </c>
       <c r="F82">
-        <v>223.2</v>
+        <v>225.99</v>
       </c>
       <c r="G82">
         <v>3.02</v>
@@ -8005,28 +8005,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M82">
-        <v>20.088</v>
+        <v>20.3391</v>
       </c>
       <c r="N82">
-        <v>12.2624081632653</v>
+        <v>12.0113081632653</v>
       </c>
       <c r="O82">
-        <v>2.575105714285713</v>
+        <v>2.522374714285713</v>
       </c>
       <c r="P82">
-        <v>9.687302448979587</v>
+        <v>9.488933448979587</v>
       </c>
       <c r="Q82">
-        <v>13.35730244897959</v>
+        <v>13.15893344897959</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.288623604798685</v>
+        <v>0.3007586407166356</v>
       </c>
       <c r="T82">
-        <v>4.094354822543632</v>
+        <v>4.298968961575103</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.610434496379197</v>
+        <v>1.59055258901649</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1147351417361607</v>
+        <v>0.1148655625125845</v>
       </c>
       <c r="C83">
-        <v>25.33329836878593</v>
+        <v>22.26285570950873</v>
       </c>
       <c r="D83">
-        <v>248.3032983687859</v>
+        <v>248.0228557095087</v>
       </c>
       <c r="E83">
-        <v>133.19</v>
+        <v>135.98</v>
       </c>
       <c r="F83">
-        <v>225.99</v>
+        <v>228.78</v>
       </c>
       <c r="G83">
         <v>3.02</v>
@@ -8087,28 +8087,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M83">
-        <v>20.3391</v>
+        <v>20.5902</v>
       </c>
       <c r="N83">
-        <v>12.0113081632653</v>
+        <v>11.7602081632653</v>
       </c>
       <c r="O83">
-        <v>2.522374714285713</v>
+        <v>2.469643714285712</v>
       </c>
       <c r="P83">
-        <v>9.488933448979587</v>
+        <v>9.290564448979584</v>
       </c>
       <c r="Q83">
-        <v>13.15893344897959</v>
+        <v>12.96056444897958</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3007586407166356</v>
+        <v>0.3142420139588027</v>
       </c>
       <c r="T83">
-        <v>4.298968961575103</v>
+        <v>4.526318004943401</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.59055258901649</v>
+        <v>1.571155606223606</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1148655625125845</v>
+        <v>0.1149959832890082</v>
       </c>
       <c r="C84">
-        <v>22.26285570950873</v>
+        <v>19.19304581957365</v>
       </c>
       <c r="D84">
-        <v>248.0228557095087</v>
+        <v>247.7430458195737</v>
       </c>
       <c r="E84">
-        <v>135.98</v>
+        <v>138.77</v>
       </c>
       <c r="F84">
-        <v>228.78</v>
+        <v>231.57</v>
       </c>
       <c r="G84">
         <v>3.02</v>
@@ -8169,28 +8169,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M84">
-        <v>20.5902</v>
+        <v>20.8413</v>
       </c>
       <c r="N84">
-        <v>11.7602081632653</v>
+        <v>11.5091081632653</v>
       </c>
       <c r="O84">
-        <v>2.469643714285712</v>
+        <v>2.416912714285713</v>
       </c>
       <c r="P84">
-        <v>9.290564448979584</v>
+        <v>9.092195448979586</v>
       </c>
       <c r="Q84">
-        <v>12.96056444897958</v>
+        <v>12.76219544897959</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3142420139588027</v>
+        <v>0.3293116664059308</v>
       </c>
       <c r="T84">
-        <v>4.526318004943401</v>
+        <v>4.780413994590325</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.571155606223606</v>
+        <v>1.552226020606454</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1149959832890082</v>
+        <v>0.115126404065432</v>
       </c>
       <c r="C85">
-        <v>19.19304581957365</v>
+        <v>16.12386655979574</v>
       </c>
       <c r="D85">
-        <v>247.7430458195737</v>
+        <v>247.4638665597957</v>
       </c>
       <c r="E85">
-        <v>138.77</v>
+        <v>141.56</v>
       </c>
       <c r="F85">
-        <v>231.57</v>
+        <v>234.36</v>
       </c>
       <c r="G85">
         <v>3.02</v>
@@ -8251,28 +8251,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M85">
-        <v>20.8413</v>
+        <v>21.0924</v>
       </c>
       <c r="N85">
-        <v>11.5091081632653</v>
+        <v>11.2580081632653</v>
       </c>
       <c r="O85">
-        <v>2.416912714285713</v>
+        <v>2.364181714285713</v>
       </c>
       <c r="P85">
-        <v>9.092195448979586</v>
+        <v>8.893826448979585</v>
       </c>
       <c r="Q85">
-        <v>12.76219544897959</v>
+        <v>12.56382644897958</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3293116664059308</v>
+        <v>0.3462650254089498</v>
       </c>
       <c r="T85">
-        <v>4.780413994590325</v>
+        <v>5.066271982943113</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.552226020606454</v>
+        <v>1.533747139408759</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.115126404065432</v>
+        <v>0.1152568248418557</v>
       </c>
       <c r="C86">
-        <v>16.12386655979577</v>
+        <v>13.0553158006214</v>
       </c>
       <c r="D86">
-        <v>247.4638665597957</v>
+        <v>247.1853158006214</v>
       </c>
       <c r="E86">
-        <v>141.56</v>
+        <v>144.35</v>
       </c>
       <c r="F86">
-        <v>234.36</v>
+        <v>237.15</v>
       </c>
       <c r="G86">
         <v>3.02</v>
@@ -8333,28 +8333,28 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M86">
-        <v>21.0924</v>
+        <v>21.3435</v>
       </c>
       <c r="N86">
-        <v>11.2580081632653</v>
+        <v>11.0069081632653</v>
       </c>
       <c r="O86">
-        <v>2.364181714285713</v>
+        <v>2.311450714285713</v>
       </c>
       <c r="P86">
-        <v>8.893826448979588</v>
+        <v>8.695457448979589</v>
       </c>
       <c r="Q86">
-        <v>12.56382644897959</v>
+        <v>12.36545744897959</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3462650254089497</v>
+        <v>0.3654788322790379</v>
       </c>
       <c r="T86">
-        <v>5.06627198294311</v>
+        <v>5.390244369742937</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.533747139408759</v>
+        <v>1.515703055415714</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1152568248418557</v>
+        <v>0.1569992604230951</v>
       </c>
       <c r="C87">
-        <v>13.0553158006214</v>
+        <v>-55.20166418354745</v>
       </c>
       <c r="D87">
-        <v>247.1853158006214</v>
+        <v>181.7183358164525</v>
       </c>
       <c r="E87">
-        <v>144.35</v>
+        <v>147.14</v>
       </c>
       <c r="F87">
-        <v>237.15</v>
+        <v>239.94</v>
       </c>
       <c r="G87">
         <v>3.02</v>
@@ -8415,45 +8415,45 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M87">
-        <v>21.3435</v>
+        <v>35.223192</v>
       </c>
       <c r="N87">
-        <v>11.0069081632653</v>
+        <v>-2.872783836734705</v>
       </c>
       <c r="O87">
-        <v>2.311450714285713</v>
+        <v>-0.603284605714288</v>
       </c>
       <c r="P87">
-        <v>8.695457448979589</v>
+        <v>-2.269499231020417</v>
       </c>
       <c r="Q87">
-        <v>12.36545744897959</v>
+        <v>1.400500768979583</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3654788322790379</v>
+        <v>0.3935787857739179</v>
       </c>
       <c r="T87">
-        <v>5.390244369742937</v>
+        <v>5.864049954667012</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.21</v>
+        <v>0.1928725174676308</v>
       </c>
       <c r="W87">
-        <v>0.0711</v>
+        <v>0.1184863144357518</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.515703055415714</v>
+        <v>0.9184405593696703</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1569992604230951</v>
+        <v>0.158009260423095</v>
       </c>
       <c r="C88">
-        <v>-55.20166418354745</v>
+        <v>-59.14875585149812</v>
       </c>
       <c r="D88">
-        <v>181.7183358164525</v>
+        <v>180.5612441485019</v>
       </c>
       <c r="E88">
-        <v>147.14</v>
+        <v>149.93</v>
       </c>
       <c r="F88">
-        <v>239.94</v>
+        <v>242.73</v>
       </c>
       <c r="G88">
         <v>3.02</v>
@@ -8497,37 +8497,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M88">
-        <v>35.223192</v>
+        <v>35.632764</v>
       </c>
       <c r="N88">
-        <v>-2.872783836734705</v>
+        <v>-3.282355836734702</v>
       </c>
       <c r="O88">
-        <v>-0.603284605714288</v>
+        <v>-0.6892947257142874</v>
       </c>
       <c r="P88">
-        <v>-2.269499231020417</v>
+        <v>-2.593061111020415</v>
       </c>
       <c r="Q88">
-        <v>1.400500768979583</v>
+        <v>1.076938888979585</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3935787857739179</v>
+        <v>0.4203310000642192</v>
       </c>
       <c r="T88">
-        <v>5.864049954667012</v>
+        <v>6.315130720410628</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1928725174676308</v>
+        <v>0.1906555919794971</v>
       </c>
       <c r="W88">
-        <v>0.1184863144357518</v>
+        <v>0.1188117590974098</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9184405593696703</v>
+        <v>0.9078837713309386</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.158009260423095</v>
+        <v>0.1590192604230951</v>
       </c>
       <c r="C89">
-        <v>-59.14875585149812</v>
+        <v>-63.08120519000673</v>
       </c>
       <c r="D89">
-        <v>180.5612441485019</v>
+        <v>179.4187948099933</v>
       </c>
       <c r="E89">
-        <v>149.93</v>
+        <v>152.72</v>
       </c>
       <c r="F89">
-        <v>242.73</v>
+        <v>245.52</v>
       </c>
       <c r="G89">
         <v>3.02</v>
@@ -8579,37 +8579,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M89">
-        <v>35.632764</v>
+        <v>36.04233600000001</v>
       </c>
       <c r="N89">
-        <v>-3.282355836734702</v>
+        <v>-3.691927836734706</v>
       </c>
       <c r="O89">
-        <v>-0.6892947257142874</v>
+        <v>-0.7753048457142883</v>
       </c>
       <c r="P89">
-        <v>-2.593061111020415</v>
+        <v>-2.916622991020418</v>
       </c>
       <c r="Q89">
-        <v>1.076938888979585</v>
+        <v>0.7533770089795819</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4203310000642192</v>
+        <v>0.4515419167362375</v>
       </c>
       <c r="T89">
-        <v>6.315130720410628</v>
+        <v>6.841391613778181</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1906555919794971</v>
+        <v>0.1884890511615482</v>
       </c>
       <c r="W89">
-        <v>0.1188117590974098</v>
+        <v>0.1191298072894847</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9078837713309386</v>
+        <v>0.8975669102930869</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1590192604230951</v>
+        <v>0.1600292604230951</v>
       </c>
       <c r="C90">
-        <v>-63.08120519000673</v>
+        <v>-66.99928838695811</v>
       </c>
       <c r="D90">
-        <v>179.4187948099933</v>
+        <v>178.2907116130419</v>
       </c>
       <c r="E90">
-        <v>152.72</v>
+        <v>155.51</v>
       </c>
       <c r="F90">
-        <v>245.52</v>
+        <v>248.31</v>
       </c>
       <c r="G90">
         <v>3.02</v>
@@ -8661,37 +8661,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M90">
-        <v>36.04233600000001</v>
+        <v>36.451908</v>
       </c>
       <c r="N90">
-        <v>-3.691927836734706</v>
+        <v>-4.101499836734703</v>
       </c>
       <c r="O90">
-        <v>-0.7753048457142883</v>
+        <v>-0.8613149657142877</v>
       </c>
       <c r="P90">
-        <v>-2.916622991020418</v>
+        <v>-3.240184871020416</v>
       </c>
       <c r="Q90">
-        <v>0.7533770089795819</v>
+        <v>0.4298151289795844</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4515419167362375</v>
+        <v>0.4884275455304409</v>
       </c>
       <c r="T90">
-        <v>6.841391613778181</v>
+        <v>7.463336305939834</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1884890511615482</v>
+        <v>0.1863711966541151</v>
       </c>
       <c r="W90">
-        <v>0.1191298072894847</v>
+        <v>0.1194407083311759</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8975669102930869</v>
+        <v>0.8874818888291196</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1600292604230951</v>
+        <v>0.161039260423095</v>
       </c>
       <c r="C91">
-        <v>-66.99928838695811</v>
+        <v>-70.90327472758833</v>
       </c>
       <c r="D91">
-        <v>178.2907116130419</v>
+        <v>177.1767252724117</v>
       </c>
       <c r="E91">
-        <v>155.51</v>
+        <v>158.3</v>
       </c>
       <c r="F91">
-        <v>248.31</v>
+        <v>251.1</v>
       </c>
       <c r="G91">
         <v>3.02</v>
@@ -8743,37 +8743,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M91">
-        <v>36.451908</v>
+        <v>36.86148</v>
       </c>
       <c r="N91">
-        <v>-4.101499836734703</v>
+        <v>-4.5110718367347</v>
       </c>
       <c r="O91">
-        <v>-0.8613149657142877</v>
+        <v>-0.9473250857142871</v>
       </c>
       <c r="P91">
-        <v>-3.240184871020416</v>
+        <v>-3.563746751020413</v>
       </c>
       <c r="Q91">
-        <v>0.4298151289795844</v>
+        <v>0.1062532489795864</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4884275455304409</v>
+        <v>0.5326903000834851</v>
       </c>
       <c r="T91">
-        <v>7.463336305939834</v>
+        <v>8.209669936533817</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1863711966541151</v>
+        <v>0.1843004055801805</v>
       </c>
       <c r="W91">
-        <v>0.1194407083311759</v>
+        <v>0.1197447004608295</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8874818888291196</v>
+        <v>0.8776209789532406</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.161039260423095</v>
+        <v>0.1620492604230951</v>
       </c>
       <c r="C92">
-        <v>-70.90327472758833</v>
+        <v>-74.79342680878983</v>
       </c>
       <c r="D92">
-        <v>177.1767252724117</v>
+        <v>176.0765731912102</v>
       </c>
       <c r="E92">
-        <v>158.3</v>
+        <v>161.09</v>
       </c>
       <c r="F92">
-        <v>251.1</v>
+        <v>253.89</v>
       </c>
       <c r="G92">
         <v>3.02</v>
@@ -8825,37 +8825,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M92">
-        <v>36.86148</v>
+        <v>37.271052</v>
       </c>
       <c r="N92">
-        <v>-4.5110718367347</v>
+        <v>-4.920643836734705</v>
       </c>
       <c r="O92">
-        <v>-0.9473250857142871</v>
+        <v>-1.033335205714288</v>
       </c>
       <c r="P92">
-        <v>-3.563746751020413</v>
+        <v>-3.887308631020417</v>
       </c>
       <c r="Q92">
-        <v>0.1062532489795864</v>
+        <v>-0.2173086310204169</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5326903000834851</v>
+        <v>0.5867892223149834</v>
       </c>
       <c r="T92">
-        <v>8.209669936533817</v>
+        <v>9.121855485037576</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1843004055801805</v>
+        <v>0.1822751263979807</v>
       </c>
       <c r="W92">
-        <v>0.1197447004608295</v>
+        <v>0.1200420114447764</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8776209789532406</v>
+        <v>0.8679767923713367</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1620492604230951</v>
+        <v>0.163059260423095</v>
       </c>
       <c r="C93">
-        <v>-74.79342680878983</v>
+        <v>-78.67000074548105</v>
       </c>
       <c r="D93">
-        <v>176.0765731912102</v>
+        <v>174.9899992545189</v>
       </c>
       <c r="E93">
-        <v>161.09</v>
+        <v>163.88</v>
       </c>
       <c r="F93">
-        <v>253.89</v>
+        <v>256.68</v>
       </c>
       <c r="G93">
         <v>3.02</v>
@@ -8907,37 +8907,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M93">
-        <v>37.271052</v>
+        <v>37.680624</v>
       </c>
       <c r="N93">
-        <v>-4.920643836734705</v>
+        <v>-5.330215836734702</v>
       </c>
       <c r="O93">
-        <v>-1.033335205714288</v>
+        <v>-1.119345325714287</v>
       </c>
       <c r="P93">
-        <v>-3.887308631020417</v>
+        <v>-4.210870511020414</v>
       </c>
       <c r="Q93">
-        <v>-0.2173086310204169</v>
+        <v>-0.5408705110204144</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5867892223149834</v>
+        <v>0.6544128751043564</v>
       </c>
       <c r="T93">
-        <v>9.121855485037576</v>
+        <v>10.26208742066727</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1822751263979807</v>
+        <v>0.1802938750240896</v>
       </c>
       <c r="W93">
-        <v>0.1200420114447764</v>
+        <v>0.1203328591464636</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8679767923713367</v>
+        <v>0.8585422620194745</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.163059260423095</v>
+        <v>0.1640692604230951</v>
       </c>
       <c r="C94">
-        <v>-78.67000074548105</v>
+        <v>-82.53324636938228</v>
       </c>
       <c r="D94">
-        <v>174.9899992545189</v>
+        <v>173.9167536306177</v>
       </c>
       <c r="E94">
-        <v>163.88</v>
+        <v>166.67</v>
       </c>
       <c r="F94">
-        <v>256.68</v>
+        <v>259.47</v>
       </c>
       <c r="G94">
         <v>3.02</v>
@@ -8989,37 +8989,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M94">
-        <v>37.680624</v>
+        <v>38.09019600000001</v>
       </c>
       <c r="N94">
-        <v>-5.330215836734702</v>
+        <v>-5.739787836734706</v>
       </c>
       <c r="O94">
-        <v>-1.119345325714287</v>
+        <v>-1.205355445714288</v>
       </c>
       <c r="P94">
-        <v>-4.210870511020414</v>
+        <v>-4.534432391020418</v>
       </c>
       <c r="Q94">
-        <v>-0.5408705110204144</v>
+        <v>-0.8644323910204177</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6544128751043564</v>
+        <v>0.7413575715478361</v>
       </c>
       <c r="T94">
-        <v>10.26208742066727</v>
+        <v>11.72809990933403</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1802938750240896</v>
+        <v>0.1783552312066263</v>
       </c>
       <c r="W94">
-        <v>0.1203328591464636</v>
+        <v>0.1206174520588673</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8585422620194745</v>
+        <v>0.8493106247934585</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1640692604230951</v>
+        <v>0.1650792604230951</v>
       </c>
       <c r="C95">
-        <v>-82.53324636938228</v>
+        <v>-86.38340742052077</v>
       </c>
       <c r="D95">
-        <v>173.9167536306177</v>
+        <v>172.8565925794792</v>
       </c>
       <c r="E95">
-        <v>166.67</v>
+        <v>169.46</v>
       </c>
       <c r="F95">
-        <v>259.47</v>
+        <v>262.26</v>
       </c>
       <c r="G95">
         <v>3.02</v>
@@ -9071,37 +9071,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M95">
-        <v>38.09019600000001</v>
+        <v>38.499768</v>
       </c>
       <c r="N95">
-        <v>-5.739787836734706</v>
+        <v>-6.149359836734703</v>
       </c>
       <c r="O95">
-        <v>-1.205355445714288</v>
+        <v>-1.291365565714288</v>
       </c>
       <c r="P95">
-        <v>-4.534432391020418</v>
+        <v>-4.857994271020416</v>
       </c>
       <c r="Q95">
-        <v>-0.8644323910204177</v>
+        <v>-1.187994271020416</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7413575715478361</v>
+        <v>0.8572838334724757</v>
       </c>
       <c r="T95">
-        <v>11.72809990933403</v>
+        <v>13.68278322755637</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1783552312066263</v>
+        <v>0.1764578351299601</v>
       </c>
       <c r="W95">
-        <v>0.1206174520588673</v>
+        <v>0.1208959898029219</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8493106247934585</v>
+        <v>0.8402754053807622</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1650792604230951</v>
+        <v>0.166089260423095</v>
       </c>
       <c r="C96">
-        <v>-86.38340742052077</v>
+        <v>-90.22072173177483</v>
       </c>
       <c r="D96">
-        <v>172.8565925794792</v>
+        <v>171.8092782682252</v>
       </c>
       <c r="E96">
-        <v>169.46</v>
+        <v>172.25</v>
       </c>
       <c r="F96">
-        <v>262.26</v>
+        <v>265.05</v>
       </c>
       <c r="G96">
         <v>3.02</v>
@@ -9153,37 +9153,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M96">
-        <v>38.499768</v>
+        <v>38.90934000000001</v>
       </c>
       <c r="N96">
-        <v>-6.149359836734703</v>
+        <v>-6.558931836734708</v>
       </c>
       <c r="O96">
-        <v>-1.291365565714288</v>
+        <v>-1.377375685714288</v>
       </c>
       <c r="P96">
-        <v>-4.857994271020416</v>
+        <v>-5.181556151020419</v>
       </c>
       <c r="Q96">
-        <v>-1.187994271020416</v>
+        <v>-1.511556151020419</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8572838334724757</v>
+        <v>1.019580600166971</v>
       </c>
       <c r="T96">
-        <v>13.68278322755637</v>
+        <v>16.41933987306765</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1764578351299601</v>
+        <v>0.1746003842338552</v>
       </c>
       <c r="W96">
-        <v>0.1208959898029219</v>
+        <v>0.1211686635944701</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8402754053807622</v>
+        <v>0.8314304011135962</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.166089260423095</v>
+        <v>0.1670992604230951</v>
       </c>
       <c r="C97">
-        <v>-90.22072173177483</v>
+        <v>-94.04542140674883</v>
       </c>
       <c r="D97">
-        <v>171.8092782682252</v>
+        <v>170.7745785932512</v>
       </c>
       <c r="E97">
-        <v>172.25</v>
+        <v>175.04</v>
       </c>
       <c r="F97">
-        <v>265.05</v>
+        <v>267.84</v>
       </c>
       <c r="G97">
         <v>3.02</v>
@@ -9235,37 +9235,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M97">
-        <v>38.90934000000001</v>
+        <v>39.31891200000001</v>
       </c>
       <c r="N97">
-        <v>-6.558931836734708</v>
+        <v>-6.968503836734712</v>
       </c>
       <c r="O97">
-        <v>-1.377375685714288</v>
+        <v>-1.463385805714289</v>
       </c>
       <c r="P97">
-        <v>-5.181556151020419</v>
+        <v>-5.505118031020422</v>
       </c>
       <c r="Q97">
-        <v>-1.511556151020419</v>
+        <v>-1.835118031020422</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.019580600166971</v>
+        <v>1.263025750208715</v>
       </c>
       <c r="T97">
-        <v>16.41933987306765</v>
+        <v>20.52417484133458</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1746003842338552</v>
+        <v>0.1727816302314192</v>
       </c>
       <c r="W97">
-        <v>0.1211686635944701</v>
+        <v>0.1214356566820277</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8314304011135962</v>
+        <v>0.8227696677686629</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1670992604230951</v>
+        <v>0.1681092604230951</v>
       </c>
       <c r="C98">
-        <v>-94.04542140674872</v>
+        <v>-97.85773299125952</v>
       </c>
       <c r="D98">
-        <v>170.7745785932512</v>
+        <v>169.7522670087405</v>
       </c>
       <c r="E98">
-        <v>175.04</v>
+        <v>177.83</v>
       </c>
       <c r="F98">
-        <v>267.84</v>
+        <v>270.63</v>
       </c>
       <c r="G98">
         <v>3.02</v>
@@ -9317,37 +9317,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M98">
-        <v>39.318912</v>
+        <v>39.728484</v>
       </c>
       <c r="N98">
-        <v>-6.968503836734698</v>
+        <v>-7.378075836734702</v>
       </c>
       <c r="O98">
-        <v>-1.463385805714287</v>
+        <v>-1.549395925714287</v>
       </c>
       <c r="P98">
-        <v>-5.505118031020411</v>
+        <v>-5.828679911020415</v>
       </c>
       <c r="Q98">
-        <v>-1.835118031020411</v>
+        <v>-2.158679911020415</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.263025750208711</v>
+        <v>1.668767666944949</v>
       </c>
       <c r="T98">
-        <v>20.52417484133452</v>
+        <v>27.3655664551127</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1727816302314192</v>
+        <v>0.1710003763115077</v>
       </c>
       <c r="W98">
-        <v>0.1214356566820277</v>
+        <v>0.1216971447574707</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8227696677686631</v>
+        <v>0.8142875062452748</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1681092604230951</v>
+        <v>0.1691192604230951</v>
       </c>
       <c r="C99">
-        <v>-97.85773299125952</v>
+        <v>-101.6578776387001</v>
       </c>
       <c r="D99">
-        <v>169.7522670087405</v>
+        <v>168.7421223612999</v>
       </c>
       <c r="E99">
-        <v>177.83</v>
+        <v>180.62</v>
       </c>
       <c r="F99">
-        <v>270.63</v>
+        <v>273.42</v>
       </c>
       <c r="G99">
         <v>3.02</v>
@@ -9399,37 +9399,37 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M99">
-        <v>39.728484</v>
+        <v>40.13805600000001</v>
       </c>
       <c r="N99">
-        <v>-7.378075836734702</v>
+        <v>-7.787647836734706</v>
       </c>
       <c r="O99">
-        <v>-1.549395925714287</v>
+        <v>-1.635406045714288</v>
       </c>
       <c r="P99">
-        <v>-5.828679911020415</v>
+        <v>-6.152241791020418</v>
       </c>
       <c r="Q99">
-        <v>-2.158679911020415</v>
+        <v>-2.482241791020418</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.668767666944949</v>
+        <v>2.480251500417423</v>
       </c>
       <c r="T99">
-        <v>27.3655664551127</v>
+        <v>41.04834968266906</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1710003763115077</v>
+        <v>0.1692554745124107</v>
       </c>
       <c r="W99">
-        <v>0.1216971447574707</v>
+        <v>0.1219532963415781</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8142875062452748</v>
+        <v>0.8059784500590984</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1691192604230951</v>
+        <v>0.2261929932777983</v>
       </c>
       <c r="C100">
-        <v>-101.6578776387001</v>
+        <v>-146.9111534569139</v>
       </c>
       <c r="D100">
-        <v>168.7421223612999</v>
+        <v>126.2788465430861</v>
       </c>
       <c r="E100">
-        <v>180.62</v>
+        <v>183.41</v>
       </c>
       <c r="F100">
-        <v>273.42</v>
+        <v>276.21</v>
       </c>
       <c r="G100">
         <v>3.02</v>
@@ -9481,129 +9481,47 @@
         <v>32.3504081632653</v>
       </c>
       <c r="M100">
-        <v>40.13805600000001</v>
+        <v>55.462968</v>
       </c>
       <c r="N100">
-        <v>-7.787647836734706</v>
+        <v>-23.1125598367347</v>
       </c>
       <c r="O100">
-        <v>-1.635406045714288</v>
+        <v>-4.853637565714286</v>
       </c>
       <c r="P100">
-        <v>-6.152241791020418</v>
+        <v>-18.25892227102041</v>
       </c>
       <c r="Q100">
-        <v>-2.482241791020418</v>
+        <v>-14.58892227102041</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.480251500417423</v>
+        <v>5.175076286305173</v>
       </c>
       <c r="T100">
-        <v>41.04834968266906</v>
+        <v>86.4869670162561</v>
       </c>
       <c r="U100">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1692554745124107</v>
+        <v>0.1224886795507538</v>
       </c>
       <c r="W100">
-        <v>0.1219532963415781</v>
+        <v>0.1762042731462087</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8059784500590984</v>
+        <v>0.583279426432161</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2261929932777983</v>
-      </c>
-      <c r="C101">
-        <v>-146.9111534569139</v>
-      </c>
-      <c r="D101">
-        <v>126.2788465430861</v>
-      </c>
-      <c r="E101">
-        <v>183.41</v>
-      </c>
-      <c r="F101">
-        <v>276.21</v>
-      </c>
-      <c r="G101">
-        <v>3.02</v>
-      </c>
-      <c r="H101">
-        <v>186.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>36.0204081632653</v>
-      </c>
-      <c r="K101">
-        <v>3.67</v>
-      </c>
-      <c r="L101">
-        <v>32.3504081632653</v>
-      </c>
-      <c r="M101">
-        <v>55.462968</v>
-      </c>
-      <c r="N101">
-        <v>-23.1125598367347</v>
-      </c>
-      <c r="O101">
-        <v>-4.853637565714286</v>
-      </c>
-      <c r="P101">
-        <v>-18.25892227102041</v>
-      </c>
-      <c r="Q101">
-        <v>-14.58892227102041</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.175076286305173</v>
-      </c>
-      <c r="T101">
-        <v>86.4869670162561</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1224886795507538</v>
-      </c>
-      <c r="W101">
-        <v>0.1762042731462087</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.583279426432161</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
